--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="459">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1123,6 +1123,18 @@
   </si>
   <si>
     <t>Анталья Сиде</t>
+  </si>
+  <si>
+    <t>22.03.26</t>
+  </si>
+  <si>
+    <t>DBD Орудия Мучения</t>
+  </si>
+  <si>
+    <t>DBD Выкованная в тумане</t>
+  </si>
+  <si>
+    <t>DBD Resident Evil: PROJECT W</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2410,7 +2422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q264"/>
+  <dimension ref="A1:Q267"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -8494,11 +8506,11 @@
         <v>334</v>
       </c>
       <c r="J194" s="21" t="str">
-        <f t="shared" ref="J194:J254" si="7">C194&amp;D194&amp;E194&amp;F194&amp;G194</f>
+        <f t="shared" ref="J194:J257" si="7">C194&amp;D194&amp;E194&amp;F194&amp;G194</f>
         <v>CupDBDGam193.PQTC.14.03.26</v>
       </c>
       <c r="L194" s="19" t="str">
-        <f t="shared" ref="L194:L254" si="8">A194&amp;" "&amp;C194&amp;D194&amp;E194&amp;F194&amp;G194&amp;" "&amp;H194</f>
+        <f t="shared" ref="L194:L257" si="8">A194&amp;" "&amp;C194&amp;D194&amp;E194&amp;F194&amp;G194&amp;" "&amp;H194</f>
         <v>193 CupDBDGam193.PQTC.14.03.26 DBD Все пороки</v>
       </c>
     </row>
@@ -10337,7 +10349,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f>A252&amp;"."</f>
+        <f t="shared" ref="E252:E264" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10369,7 +10381,7 @@
         <v>338</v>
       </c>
       <c r="E253" s="6" t="str">
-        <f>A253&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>252.</v>
       </c>
       <c r="F253" s="19" t="s">
@@ -10401,7 +10413,7 @@
         <v>338</v>
       </c>
       <c r="E254" s="6" t="str">
-        <f>A254&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>253.</v>
       </c>
       <c r="F254" s="19" t="s">
@@ -10433,7 +10445,7 @@
         <v>338</v>
       </c>
       <c r="E255" s="6" t="str">
-        <f>A255&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>254.</v>
       </c>
       <c r="F255" s="19" t="s">
@@ -10446,11 +10458,11 @@
         <v>359</v>
       </c>
       <c r="J255" s="21" t="str">
-        <f>C255&amp;D255&amp;E255&amp;F255&amp;G255</f>
+        <f t="shared" si="7"/>
         <v>NtrAntaly254.PQTC.21.03.26</v>
       </c>
       <c r="L255" s="19" t="str">
-        <f>A255&amp;" "&amp;C255&amp;D255&amp;E255&amp;F255&amp;G255&amp;" "&amp;H255</f>
+        <f t="shared" si="8"/>
         <v>254 NtrAntaly254.PQTC.21.03.26 Анталья Фаселис</v>
       </c>
     </row>
@@ -10465,7 +10477,7 @@
         <v>338</v>
       </c>
       <c r="E256" s="6" t="str">
-        <f>A256&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>255.</v>
       </c>
       <c r="F256" s="19" t="s">
@@ -10478,11 +10490,11 @@
         <v>358</v>
       </c>
       <c r="J256" s="21" t="str">
-        <f>C256&amp;D256&amp;E256&amp;F256&amp;G256</f>
+        <f t="shared" si="7"/>
         <v>NtrAntaly255.PQTC.21.03.26</v>
       </c>
       <c r="L256" s="19" t="str">
-        <f>A256&amp;" "&amp;C256&amp;D256&amp;E256&amp;F256&amp;G256&amp;" "&amp;H256</f>
+        <f t="shared" si="8"/>
         <v>255 NtrAntaly255.PQTC.21.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -10497,7 +10509,7 @@
         <v>338</v>
       </c>
       <c r="E257" s="6" t="str">
-        <f>A257&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>256.</v>
       </c>
       <c r="F257" s="19" t="s">
@@ -10510,11 +10522,11 @@
         <v>358</v>
       </c>
       <c r="J257" s="21" t="str">
-        <f>C257&amp;D257&amp;E257&amp;F257&amp;G257</f>
+        <f t="shared" si="7"/>
         <v>NtrAntaly256.PQTC.21.03.26</v>
       </c>
       <c r="L257" s="19" t="str">
-        <f>A257&amp;" "&amp;C257&amp;D257&amp;E257&amp;F257&amp;G257&amp;" "&amp;H257</f>
+        <f t="shared" si="8"/>
         <v>256 NtrAntaly256.PQTC.21.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -10529,7 +10541,7 @@
         <v>338</v>
       </c>
       <c r="E258" s="6" t="str">
-        <f>A258&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>257.</v>
       </c>
       <c r="F258" s="19" t="s">
@@ -10542,11 +10554,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f>C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J264" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f>A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L264" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -10561,7 +10573,7 @@
         <v>338</v>
       </c>
       <c r="E259" s="6" t="str">
-        <f>A259&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>258.</v>
       </c>
       <c r="F259" s="19" t="s">
@@ -10574,11 +10586,11 @@
         <v>364</v>
       </c>
       <c r="J259" s="21" t="str">
-        <f>C259&amp;D259&amp;E259&amp;F259&amp;G259</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly258.PQTC.21.03.26</v>
       </c>
       <c r="L259" s="19" t="str">
-        <f>A259&amp;" "&amp;C259&amp;D259&amp;E259&amp;F259&amp;G259&amp;" "&amp;H259</f>
+        <f t="shared" si="11"/>
         <v>258 NtrAntaly258.PQTC.21.03.26 Анталья Сиде</v>
       </c>
     </row>
@@ -10593,7 +10605,7 @@
         <v>338</v>
       </c>
       <c r="E260" s="6" t="str">
-        <f>A260&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>259.</v>
       </c>
       <c r="F260" s="19" t="s">
@@ -10606,11 +10618,11 @@
         <v>358</v>
       </c>
       <c r="J260" s="21" t="str">
-        <f>C260&amp;D260&amp;E260&amp;F260&amp;G260</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly259.PQTC.21.03.26</v>
       </c>
       <c r="L260" s="19" t="str">
-        <f>A260&amp;" "&amp;C260&amp;D260&amp;E260&amp;F260&amp;G260&amp;" "&amp;H260</f>
+        <f t="shared" si="11"/>
         <v>259 NtrAntaly259.PQTC.21.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -10625,7 +10637,7 @@
         <v>338</v>
       </c>
       <c r="E261" s="6" t="str">
-        <f>A261&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>260.</v>
       </c>
       <c r="F261" s="19" t="s">
@@ -10638,11 +10650,11 @@
         <v>360</v>
       </c>
       <c r="J261" s="21" t="str">
-        <f>C261&amp;D261&amp;E261&amp;F261&amp;G261</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly260.PQTC.21.03.26</v>
       </c>
       <c r="L261" s="19" t="str">
-        <f>A261&amp;" "&amp;C261&amp;D261&amp;E261&amp;F261&amp;G261&amp;" "&amp;H261</f>
+        <f t="shared" si="11"/>
         <v>260 NtrAntaly260.PQTC.21.03.26 Анталья Аспендос</v>
       </c>
     </row>
@@ -10657,7 +10669,7 @@
         <v>338</v>
       </c>
       <c r="E262" s="6" t="str">
-        <f>A262&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>261.</v>
       </c>
       <c r="F262" s="19" t="s">
@@ -10670,11 +10682,11 @@
         <v>360</v>
       </c>
       <c r="J262" s="21" t="str">
-        <f>C262&amp;D262&amp;E262&amp;F262&amp;G262</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly261.PQTC.21.03.26</v>
       </c>
       <c r="L262" s="19" t="str">
-        <f>A262&amp;" "&amp;C262&amp;D262&amp;E262&amp;F262&amp;G262&amp;" "&amp;H262</f>
+        <f t="shared" si="11"/>
         <v>261 NtrAntaly261.PQTC.21.03.26 Анталья Аспендос</v>
       </c>
     </row>
@@ -10689,7 +10701,7 @@
         <v>338</v>
       </c>
       <c r="E263" s="6" t="str">
-        <f>A263&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>262.</v>
       </c>
       <c r="F263" s="19" t="s">
@@ -10702,11 +10714,11 @@
         <v>359</v>
       </c>
       <c r="J263" s="21" t="str">
-        <f>C263&amp;D263&amp;E263&amp;F263&amp;G263</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly262.PQTC.21.03.26</v>
       </c>
       <c r="L263" s="19" t="str">
-        <f>A263&amp;" "&amp;C263&amp;D263&amp;E263&amp;F263&amp;G263&amp;" "&amp;H263</f>
+        <f t="shared" si="11"/>
         <v>262 NtrAntaly262.PQTC.21.03.26 Анталья Фаселис</v>
       </c>
     </row>
@@ -10721,7 +10733,7 @@
         <v>338</v>
       </c>
       <c r="E264" s="6" t="str">
-        <f>A264&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>263.</v>
       </c>
       <c r="F264" s="19" t="s">
@@ -10734,12 +10746,108 @@
         <v>364</v>
       </c>
       <c r="J264" s="21" t="str">
-        <f>C264&amp;D264&amp;E264&amp;F264&amp;G264</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly263.PQTC.21.03.26</v>
       </c>
       <c r="L264" s="19" t="str">
-        <f>A264&amp;" "&amp;C264&amp;D264&amp;E264&amp;F264&amp;G264&amp;" "&amp;H264</f>
+        <f t="shared" si="11"/>
         <v>263 NtrAntaly263.PQTC.21.03.26 Анталья Сиде</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12">
+      <c r="A265" s="5">
+        <v>264</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D265" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E265" s="6" t="str">
+        <f>A265&amp;"."</f>
+        <v>264.</v>
+      </c>
+      <c r="F265" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H265" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="J265" s="21" t="str">
+        <f>C265&amp;D265&amp;E265&amp;F265&amp;G265</f>
+        <v>CupDBDGam264.PQTC.22.03.26</v>
+      </c>
+      <c r="L265" s="19" t="str">
+        <f>A265&amp;" "&amp;C265&amp;D265&amp;E265&amp;F265&amp;G265&amp;" "&amp;H265</f>
+        <v>264 CupDBDGam264.PQTC.22.03.26 DBD Орудия Мучения</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12">
+      <c r="A266" s="5">
+        <v>265</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E266" s="6" t="str">
+        <f>A266&amp;"."</f>
+        <v>265.</v>
+      </c>
+      <c r="F266" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H266" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="J266" s="21" t="str">
+        <f>C266&amp;D266&amp;E266&amp;F266&amp;G266</f>
+        <v>CupDBDGam265.PQTC.22.03.26</v>
+      </c>
+      <c r="L266" s="19" t="str">
+        <f>A266&amp;" "&amp;C266&amp;D266&amp;E266&amp;F266&amp;G266&amp;" "&amp;H266</f>
+        <v>265 CupDBDGam265.PQTC.22.03.26 DBD Выкованная в тумане</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12">
+      <c r="A267" s="5">
+        <v>266</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E267" s="6" t="str">
+        <f>A267&amp;"."</f>
+        <v>266.</v>
+      </c>
+      <c r="F267" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H267" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="J267" s="21" t="str">
+        <f>C267&amp;D267&amp;E267&amp;F267&amp;G267</f>
+        <v>CupDBDGam266.PQTC.22.03.26</v>
+      </c>
+      <c r="L267" s="19" t="str">
+        <f>A267&amp;" "&amp;C267&amp;D267&amp;E267&amp;F267&amp;G267&amp;" "&amp;H267</f>
+        <v>266 CupDBDGam266.PQTC.22.03.26 DBD Resident Evil: PROJECT W</v>
       </c>
     </row>
   </sheetData>
@@ -10797,127 +10905,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -10925,23 +11033,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -10949,23 +11057,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -10973,39 +11081,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -11013,162 +11121,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="460">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1135,6 +1135,9 @@
   </si>
   <si>
     <t>DBD Resident Evil: PROJECT W</t>
+  </si>
+  <si>
+    <t>Анталья Аланья</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2422,7 +2425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q267"/>
+  <dimension ref="A1:Q279"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -10349,7 +10352,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" ref="E252:E264" si="9">A252&amp;"."</f>
+        <f t="shared" ref="E252:E267" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10554,11 +10557,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" ref="J258:J264" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J267" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f t="shared" ref="L258:L264" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L267" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -10765,7 +10768,7 @@
         <v>316</v>
       </c>
       <c r="E265" s="6" t="str">
-        <f>A265&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>264.</v>
       </c>
       <c r="F265" s="19" t="s">
@@ -10778,11 +10781,11 @@
         <v>366</v>
       </c>
       <c r="J265" s="21" t="str">
-        <f>C265&amp;D265&amp;E265&amp;F265&amp;G265</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam264.PQTC.22.03.26</v>
       </c>
       <c r="L265" s="19" t="str">
-        <f>A265&amp;" "&amp;C265&amp;D265&amp;E265&amp;F265&amp;G265&amp;" "&amp;H265</f>
+        <f t="shared" si="11"/>
         <v>264 CupDBDGam264.PQTC.22.03.26 DBD Орудия Мучения</v>
       </c>
     </row>
@@ -10797,7 +10800,7 @@
         <v>316</v>
       </c>
       <c r="E266" s="6" t="str">
-        <f>A266&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>265.</v>
       </c>
       <c r="F266" s="19" t="s">
@@ -10810,11 +10813,11 @@
         <v>367</v>
       </c>
       <c r="J266" s="21" t="str">
-        <f>C266&amp;D266&amp;E266&amp;F266&amp;G266</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam265.PQTC.22.03.26</v>
       </c>
       <c r="L266" s="19" t="str">
-        <f>A266&amp;" "&amp;C266&amp;D266&amp;E266&amp;F266&amp;G266&amp;" "&amp;H266</f>
+        <f t="shared" si="11"/>
         <v>265 CupDBDGam265.PQTC.22.03.26 DBD Выкованная в тумане</v>
       </c>
     </row>
@@ -10829,7 +10832,7 @@
         <v>316</v>
       </c>
       <c r="E267" s="6" t="str">
-        <f>A267&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>266.</v>
       </c>
       <c r="F267" s="19" t="s">
@@ -10842,12 +10845,396 @@
         <v>368</v>
       </c>
       <c r="J267" s="21" t="str">
-        <f>C267&amp;D267&amp;E267&amp;F267&amp;G267</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam266.PQTC.22.03.26</v>
       </c>
       <c r="L267" s="19" t="str">
-        <f>A267&amp;" "&amp;C267&amp;D267&amp;E267&amp;F267&amp;G267&amp;" "&amp;H267</f>
+        <f t="shared" si="11"/>
         <v>266 CupDBDGam266.PQTC.22.03.26 DBD Resident Evil: PROJECT W</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12">
+      <c r="A268" s="5">
+        <v>267</v>
+      </c>
+      <c r="C268" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D268" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E268" s="6" t="str">
+        <f>A268&amp;"."</f>
+        <v>267.</v>
+      </c>
+      <c r="F268" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H268" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="J268" s="21" t="str">
+        <f>C268&amp;D268&amp;E268&amp;F268&amp;G268</f>
+        <v>NtrAntaly267.PQTC.22.03.26</v>
+      </c>
+      <c r="L268" s="19" t="str">
+        <f>A268&amp;" "&amp;C268&amp;D268&amp;E268&amp;F268&amp;G268&amp;" "&amp;H268</f>
+        <v>267 NtrAntaly267.PQTC.22.03.26 Анталья Аланья</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12">
+      <c r="A269" s="5">
+        <v>268</v>
+      </c>
+      <c r="C269" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D269" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E269" s="6" t="str">
+        <f>A269&amp;"."</f>
+        <v>268.</v>
+      </c>
+      <c r="F269" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H269" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="J269" s="21" t="str">
+        <f>C269&amp;D269&amp;E269&amp;F269&amp;G269</f>
+        <v>NtrAntaly268.PQTC.22.03.26</v>
+      </c>
+      <c r="L269" s="19" t="str">
+        <f>A269&amp;" "&amp;C269&amp;D269&amp;E269&amp;F269&amp;G269&amp;" "&amp;H269</f>
+        <v>268 NtrAntaly268.PQTC.22.03.26 Анталья Сиде</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12">
+      <c r="A270" s="5">
+        <v>269</v>
+      </c>
+      <c r="C270" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D270" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E270" s="6" t="str">
+        <f>A270&amp;"."</f>
+        <v>269.</v>
+      </c>
+      <c r="F270" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H270" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J270" s="21" t="str">
+        <f>C270&amp;D270&amp;E270&amp;F270&amp;G270</f>
+        <v>NtrAntaly269.PQTC.22.03.26</v>
+      </c>
+      <c r="L270" s="19" t="str">
+        <f>A270&amp;" "&amp;C270&amp;D270&amp;E270&amp;F270&amp;G270&amp;" "&amp;H270</f>
+        <v>269 NtrAntaly269.PQTC.22.03.26 Анталья Перге</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12">
+      <c r="A271" s="5">
+        <v>270</v>
+      </c>
+      <c r="C271" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D271" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E271" s="6" t="str">
+        <f>A271&amp;"."</f>
+        <v>270.</v>
+      </c>
+      <c r="F271" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H271" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="J271" s="21" t="str">
+        <f>C271&amp;D271&amp;E271&amp;F271&amp;G271</f>
+        <v>NtrAntaly270.PQTC.22.03.26</v>
+      </c>
+      <c r="L271" s="19" t="str">
+        <f>A271&amp;" "&amp;C271&amp;D271&amp;E271&amp;F271&amp;G271&amp;" "&amp;H271</f>
+        <v>270 NtrAntaly270.PQTC.22.03.26 Анталья Аспендос</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12">
+      <c r="A272" s="5">
+        <v>271</v>
+      </c>
+      <c r="C272" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E272" s="6" t="str">
+        <f>A272&amp;"."</f>
+        <v>271.</v>
+      </c>
+      <c r="F272" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H272" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J272" s="21" t="str">
+        <f>C272&amp;D272&amp;E272&amp;F272&amp;G272</f>
+        <v>NtrAntaly271.PQTC.22.03.26</v>
+      </c>
+      <c r="L272" s="19" t="str">
+        <f>A272&amp;" "&amp;C272&amp;D272&amp;E272&amp;F272&amp;G272&amp;" "&amp;H272</f>
+        <v>271 NtrAntaly271.PQTC.22.03.26 Анталья Фаселис</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12">
+      <c r="A273" s="5">
+        <v>272</v>
+      </c>
+      <c r="C273" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D273" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E273" s="6" t="str">
+        <f>A273&amp;"."</f>
+        <v>272.</v>
+      </c>
+      <c r="F273" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H273" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J273" s="21" t="str">
+        <f>C273&amp;D273&amp;E273&amp;F273&amp;G273</f>
+        <v>NtrAntaly272.PQTC.22.03.26</v>
+      </c>
+      <c r="L273" s="19" t="str">
+        <f>A273&amp;" "&amp;C273&amp;D273&amp;E273&amp;F273&amp;G273&amp;" "&amp;H273</f>
+        <v>272 NtrAntaly272.PQTC.22.03.26 Анталья Фаселис</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12">
+      <c r="A274" s="5">
+        <v>273</v>
+      </c>
+      <c r="C274" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E274" s="6" t="str">
+        <f>A274&amp;"."</f>
+        <v>273.</v>
+      </c>
+      <c r="F274" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H274" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="J274" s="21" t="str">
+        <f>C274&amp;D274&amp;E274&amp;F274&amp;G274</f>
+        <v>NtrAntaly273.PQTC.22.03.26</v>
+      </c>
+      <c r="L274" s="19" t="str">
+        <f>A274&amp;" "&amp;C274&amp;D274&amp;E274&amp;F274&amp;G274&amp;" "&amp;H274</f>
+        <v>273 NtrAntaly273.PQTC.22.03.26 Анталья храм Аполлона Сиде</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12">
+      <c r="A275" s="5">
+        <v>274</v>
+      </c>
+      <c r="C275" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D275" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E275" s="6" t="str">
+        <f>A275&amp;"."</f>
+        <v>274.</v>
+      </c>
+      <c r="F275" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H275" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J275" s="21" t="str">
+        <f>C275&amp;D275&amp;E275&amp;F275&amp;G275</f>
+        <v>NtrAntaly274.PQTC.22.03.26</v>
+      </c>
+      <c r="L275" s="19" t="str">
+        <f>A275&amp;" "&amp;C275&amp;D275&amp;E275&amp;F275&amp;G275&amp;" "&amp;H275</f>
+        <v>274 NtrAntaly274.PQTC.22.03.26 Анталья Перге</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12">
+      <c r="A276" s="5">
+        <v>275</v>
+      </c>
+      <c r="C276" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D276" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E276" s="6" t="str">
+        <f>A276&amp;"."</f>
+        <v>275.</v>
+      </c>
+      <c r="F276" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H276" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J276" s="21" t="str">
+        <f>C276&amp;D276&amp;E276&amp;F276&amp;G276</f>
+        <v>NtrAntaly275.PQTC.22.03.26</v>
+      </c>
+      <c r="L276" s="19" t="str">
+        <f>A276&amp;" "&amp;C276&amp;D276&amp;E276&amp;F276&amp;G276&amp;" "&amp;H276</f>
+        <v>275 NtrAntaly275.PQTC.22.03.26 Анталья Фаселис</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12">
+      <c r="A277" s="5">
+        <v>276</v>
+      </c>
+      <c r="C277" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D277" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E277" s="6" t="str">
+        <f>A277&amp;"."</f>
+        <v>276.</v>
+      </c>
+      <c r="F277" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H277" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="J277" s="21" t="str">
+        <f>C277&amp;D277&amp;E277&amp;F277&amp;G277</f>
+        <v>NtrAntaly276.PQTC.22.03.26</v>
+      </c>
+      <c r="L277" s="19" t="str">
+        <f>A277&amp;" "&amp;C277&amp;D277&amp;E277&amp;F277&amp;G277&amp;" "&amp;H277</f>
+        <v>276 NtrAntaly276.PQTC.22.03.26 Анталья Аспендос</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12">
+      <c r="A278" s="5">
+        <v>277</v>
+      </c>
+      <c r="C278" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D278" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E278" s="6" t="str">
+        <f>A278&amp;"."</f>
+        <v>277.</v>
+      </c>
+      <c r="F278" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H278" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J278" s="21" t="str">
+        <f>C278&amp;D278&amp;E278&amp;F278&amp;G278</f>
+        <v>NtrAntaly277.PQTC.22.03.26</v>
+      </c>
+      <c r="L278" s="19" t="str">
+        <f>A278&amp;" "&amp;C278&amp;D278&amp;E278&amp;F278&amp;G278&amp;" "&amp;H278</f>
+        <v>277 NtrAntaly277.PQTC.22.03.26 Анталья Перге</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12">
+      <c r="A279" s="5">
+        <v>278</v>
+      </c>
+      <c r="C279" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D279" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E279" s="6" t="str">
+        <f>A279&amp;"."</f>
+        <v>278.</v>
+      </c>
+      <c r="F279" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H279" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J279" s="21" t="str">
+        <f>C279&amp;D279&amp;E279&amp;F279&amp;G279</f>
+        <v>NtrAntaly278.PQTC.22.03.26</v>
+      </c>
+      <c r="L279" s="19" t="str">
+        <f>A279&amp;" "&amp;C279&amp;D279&amp;E279&amp;F279&amp;G279&amp;" "&amp;H279</f>
+        <v>278 NtrAntaly278.PQTC.22.03.26 Анталья Перге</v>
       </c>
     </row>
   </sheetData>
@@ -10905,127 +11292,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -11033,23 +11420,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -11057,23 +11444,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -11081,39 +11468,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -11121,162 +11508,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="462">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1125,19 +1125,25 @@
     <t>Анталья Сиде</t>
   </si>
   <si>
+    <t>24.03.26</t>
+  </si>
+  <si>
+    <t>DBD Орудия Мучения</t>
+  </si>
+  <si>
+    <t>DBD Выкованная в тумане</t>
+  </si>
+  <si>
+    <t>DBD Resident Evil: PROJECT W</t>
+  </si>
+  <si>
     <t>22.03.26</t>
   </si>
   <si>
-    <t>DBD Орудия Мучения</t>
-  </si>
-  <si>
-    <t>DBD Выкованная в тумане</t>
-  </si>
-  <si>
-    <t>DBD Resident Evil: PROJECT W</t>
-  </si>
-  <si>
     <t>Анталья Аланья</t>
+  </si>
+  <si>
+    <t>Анталья Ликийские гробницы</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2425,7 +2431,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q279"/>
+  <dimension ref="A1:Q280"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -10352,7 +10358,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" ref="E252:E267" si="9">A252&amp;"."</f>
+        <f t="shared" ref="E252:E279" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10557,11 +10563,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" ref="J258:J267" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J279" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f t="shared" ref="L258:L267" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L279" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -10782,11 +10788,11 @@
       </c>
       <c r="J265" s="21" t="str">
         <f t="shared" si="10"/>
-        <v>CupDBDGam264.PQTC.22.03.26</v>
+        <v>CupDBDGam264.PQTC.24.03.26</v>
       </c>
       <c r="L265" s="19" t="str">
         <f t="shared" si="11"/>
-        <v>264 CupDBDGam264.PQTC.22.03.26 DBD Орудия Мучения</v>
+        <v>264 CupDBDGam264.PQTC.24.03.26 DBD Орудия Мучения</v>
       </c>
     </row>
     <row r="266" spans="1:12">
@@ -10814,11 +10820,11 @@
       </c>
       <c r="J266" s="21" t="str">
         <f t="shared" si="10"/>
-        <v>CupDBDGam265.PQTC.22.03.26</v>
+        <v>CupDBDGam265.PQTC.24.03.26</v>
       </c>
       <c r="L266" s="19" t="str">
         <f t="shared" si="11"/>
-        <v>265 CupDBDGam265.PQTC.22.03.26 DBD Выкованная в тумане</v>
+        <v>265 CupDBDGam265.PQTC.24.03.26 DBD Выкованная в тумане</v>
       </c>
     </row>
     <row r="267" spans="1:12">
@@ -10846,11 +10852,11 @@
       </c>
       <c r="J267" s="21" t="str">
         <f t="shared" si="10"/>
-        <v>CupDBDGam266.PQTC.22.03.26</v>
+        <v>CupDBDGam266.PQTC.24.03.26</v>
       </c>
       <c r="L267" s="19" t="str">
         <f t="shared" si="11"/>
-        <v>266 CupDBDGam266.PQTC.22.03.26 DBD Resident Evil: PROJECT W</v>
+        <v>266 CupDBDGam266.PQTC.24.03.26 DBD Resident Evil: PROJECT W</v>
       </c>
     </row>
     <row r="268" spans="1:12">
@@ -10864,24 +10870,24 @@
         <v>338</v>
       </c>
       <c r="E268" s="6" t="str">
-        <f>A268&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>267.</v>
       </c>
       <c r="F268" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H268" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J268" s="21" t="str">
-        <f>C268&amp;D268&amp;E268&amp;F268&amp;G268</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly267.PQTC.22.03.26</v>
       </c>
       <c r="L268" s="19" t="str">
-        <f>A268&amp;" "&amp;C268&amp;D268&amp;E268&amp;F268&amp;G268&amp;" "&amp;H268</f>
+        <f t="shared" si="11"/>
         <v>267 NtrAntaly267.PQTC.22.03.26 Анталья Аланья</v>
       </c>
     </row>
@@ -10896,24 +10902,24 @@
         <v>338</v>
       </c>
       <c r="E269" s="6" t="str">
-        <f>A269&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>268.</v>
       </c>
       <c r="F269" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H269" s="6" t="s">
         <v>364</v>
       </c>
       <c r="J269" s="21" t="str">
-        <f>C269&amp;D269&amp;E269&amp;F269&amp;G269</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly268.PQTC.22.03.26</v>
       </c>
       <c r="L269" s="19" t="str">
-        <f>A269&amp;" "&amp;C269&amp;D269&amp;E269&amp;F269&amp;G269&amp;" "&amp;H269</f>
+        <f t="shared" si="11"/>
         <v>268 NtrAntaly268.PQTC.22.03.26 Анталья Сиде</v>
       </c>
     </row>
@@ -10928,24 +10934,24 @@
         <v>338</v>
       </c>
       <c r="E270" s="6" t="str">
-        <f>A270&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>269.</v>
       </c>
       <c r="F270" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G270" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H270" s="6" t="s">
         <v>358</v>
       </c>
       <c r="J270" s="21" t="str">
-        <f>C270&amp;D270&amp;E270&amp;F270&amp;G270</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly269.PQTC.22.03.26</v>
       </c>
       <c r="L270" s="19" t="str">
-        <f>A270&amp;" "&amp;C270&amp;D270&amp;E270&amp;F270&amp;G270&amp;" "&amp;H270</f>
+        <f t="shared" si="11"/>
         <v>269 NtrAntaly269.PQTC.22.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -10960,24 +10966,24 @@
         <v>338</v>
       </c>
       <c r="E271" s="6" t="str">
-        <f>A271&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>270.</v>
       </c>
       <c r="F271" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G271" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H271" s="6" t="s">
         <v>360</v>
       </c>
       <c r="J271" s="21" t="str">
-        <f>C271&amp;D271&amp;E271&amp;F271&amp;G271</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly270.PQTC.22.03.26</v>
       </c>
       <c r="L271" s="19" t="str">
-        <f>A271&amp;" "&amp;C271&amp;D271&amp;E271&amp;F271&amp;G271&amp;" "&amp;H271</f>
+        <f t="shared" si="11"/>
         <v>270 NtrAntaly270.PQTC.22.03.26 Анталья Аспендос</v>
       </c>
     </row>
@@ -10992,24 +10998,24 @@
         <v>338</v>
       </c>
       <c r="E272" s="6" t="str">
-        <f>A272&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>271.</v>
       </c>
       <c r="F272" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G272" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>359</v>
       </c>
       <c r="J272" s="21" t="str">
-        <f>C272&amp;D272&amp;E272&amp;F272&amp;G272</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly271.PQTC.22.03.26</v>
       </c>
       <c r="L272" s="19" t="str">
-        <f>A272&amp;" "&amp;C272&amp;D272&amp;E272&amp;F272&amp;G272&amp;" "&amp;H272</f>
+        <f t="shared" si="11"/>
         <v>271 NtrAntaly271.PQTC.22.03.26 Анталья Фаселис</v>
       </c>
     </row>
@@ -11024,24 +11030,24 @@
         <v>338</v>
       </c>
       <c r="E273" s="6" t="str">
-        <f>A273&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>272.</v>
       </c>
       <c r="F273" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G273" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>359</v>
       </c>
       <c r="J273" s="21" t="str">
-        <f>C273&amp;D273&amp;E273&amp;F273&amp;G273</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly272.PQTC.22.03.26</v>
       </c>
       <c r="L273" s="19" t="str">
-        <f>A273&amp;" "&amp;C273&amp;D273&amp;E273&amp;F273&amp;G273&amp;" "&amp;H273</f>
+        <f t="shared" si="11"/>
         <v>272 NtrAntaly272.PQTC.22.03.26 Анталья Фаселис</v>
       </c>
     </row>
@@ -11056,24 +11062,24 @@
         <v>338</v>
       </c>
       <c r="E274" s="6" t="str">
-        <f>A274&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>273.</v>
       </c>
       <c r="F274" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>363</v>
       </c>
       <c r="J274" s="21" t="str">
-        <f>C274&amp;D274&amp;E274&amp;F274&amp;G274</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly273.PQTC.22.03.26</v>
       </c>
       <c r="L274" s="19" t="str">
-        <f>A274&amp;" "&amp;C274&amp;D274&amp;E274&amp;F274&amp;G274&amp;" "&amp;H274</f>
+        <f t="shared" si="11"/>
         <v>273 NtrAntaly273.PQTC.22.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -11088,24 +11094,24 @@
         <v>338</v>
       </c>
       <c r="E275" s="6" t="str">
-        <f>A275&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>274.</v>
       </c>
       <c r="F275" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G275" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H275" s="6" t="s">
         <v>358</v>
       </c>
       <c r="J275" s="21" t="str">
-        <f>C275&amp;D275&amp;E275&amp;F275&amp;G275</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly274.PQTC.22.03.26</v>
       </c>
       <c r="L275" s="19" t="str">
-        <f>A275&amp;" "&amp;C275&amp;D275&amp;E275&amp;F275&amp;G275&amp;" "&amp;H275</f>
+        <f t="shared" si="11"/>
         <v>274 NtrAntaly274.PQTC.22.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -11120,24 +11126,24 @@
         <v>338</v>
       </c>
       <c r="E276" s="6" t="str">
-        <f>A276&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>275.</v>
       </c>
       <c r="F276" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G276" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>359</v>
       </c>
       <c r="J276" s="21" t="str">
-        <f>C276&amp;D276&amp;E276&amp;F276&amp;G276</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly275.PQTC.22.03.26</v>
       </c>
       <c r="L276" s="19" t="str">
-        <f>A276&amp;" "&amp;C276&amp;D276&amp;E276&amp;F276&amp;G276&amp;" "&amp;H276</f>
+        <f t="shared" si="11"/>
         <v>275 NtrAntaly275.PQTC.22.03.26 Анталья Фаселис</v>
       </c>
     </row>
@@ -11152,24 +11158,24 @@
         <v>338</v>
       </c>
       <c r="E277" s="6" t="str">
-        <f>A277&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>276.</v>
       </c>
       <c r="F277" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G277" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>360</v>
       </c>
       <c r="J277" s="21" t="str">
-        <f>C277&amp;D277&amp;E277&amp;F277&amp;G277</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly276.PQTC.22.03.26</v>
       </c>
       <c r="L277" s="19" t="str">
-        <f>A277&amp;" "&amp;C277&amp;D277&amp;E277&amp;F277&amp;G277&amp;" "&amp;H277</f>
+        <f t="shared" si="11"/>
         <v>276 NtrAntaly276.PQTC.22.03.26 Анталья Аспендос</v>
       </c>
     </row>
@@ -11184,24 +11190,24 @@
         <v>338</v>
       </c>
       <c r="E278" s="6" t="str">
-        <f>A278&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>277.</v>
       </c>
       <c r="F278" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G278" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>358</v>
       </c>
       <c r="J278" s="21" t="str">
-        <f>C278&amp;D278&amp;E278&amp;F278&amp;G278</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly277.PQTC.22.03.26</v>
       </c>
       <c r="L278" s="19" t="str">
-        <f>A278&amp;" "&amp;C278&amp;D278&amp;E278&amp;F278&amp;G278&amp;" "&amp;H278</f>
+        <f t="shared" si="11"/>
         <v>277 NtrAntaly277.PQTC.22.03.26 Анталья Перге</v>
       </c>
     </row>
@@ -11216,25 +11222,57 @@
         <v>338</v>
       </c>
       <c r="E279" s="6" t="str">
-        <f>A279&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>278.</v>
       </c>
       <c r="F279" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G279" s="8" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H279" s="6" t="s">
         <v>358</v>
       </c>
       <c r="J279" s="21" t="str">
-        <f>C279&amp;D279&amp;E279&amp;F279&amp;G279</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly278.PQTC.22.03.26</v>
       </c>
       <c r="L279" s="19" t="str">
-        <f>A279&amp;" "&amp;C279&amp;D279&amp;E279&amp;F279&amp;G279&amp;" "&amp;H279</f>
+        <f t="shared" si="11"/>
         <v>278 NtrAntaly278.PQTC.22.03.26 Анталья Перге</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12">
+      <c r="A280" s="5">
+        <v>279</v>
+      </c>
+      <c r="C280" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E280" s="6" t="str">
+        <f>A280&amp;"."</f>
+        <v>279.</v>
+      </c>
+      <c r="F280" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H280" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="J280" s="21" t="str">
+        <f>C280&amp;D280&amp;E280&amp;F280&amp;G280</f>
+        <v>NtrAntaly279.PQTC.24.03.26</v>
+      </c>
+      <c r="L280" s="19" t="str">
+        <f>A280&amp;" "&amp;C280&amp;D280&amp;E280&amp;F280&amp;G280&amp;" "&amp;H280</f>
+        <v>279 NtrAntaly279.PQTC.24.03.26 Анталья Ликийские гробницы</v>
       </c>
     </row>
   </sheetData>
@@ -11292,127 +11330,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -11420,23 +11458,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -11444,23 +11482,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -11468,39 +11506,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -11508,162 +11546,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="483">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1144,6 +1144,69 @@
   </si>
   <si>
     <t>Анталья Ликийские гробницы</t>
+  </si>
+  <si>
+    <t>DBD Корни ужаса</t>
+  </si>
+  <si>
+    <t>DBD Восход Садако</t>
+  </si>
+  <si>
+    <t>DBD Resident Evil</t>
+  </si>
+  <si>
+    <t>DBD Узы родства</t>
+  </si>
+  <si>
+    <t>DBD Спуск в преисподнюю</t>
+  </si>
+  <si>
+    <t>DBD Сайлент Хилл</t>
+  </si>
+  <si>
+    <t>DBD Цепи ненависти</t>
+  </si>
+  <si>
+    <t>DBD Проклятое наследие</t>
+  </si>
+  <si>
+    <t>DBD Конец верных</t>
+  </si>
+  <si>
+    <t>DBD Тьма среди нас</t>
+  </si>
+  <si>
+    <t>DBD Расколотая родословная</t>
+  </si>
+  <si>
+    <t>DBD Занавес</t>
+  </si>
+  <si>
+    <t>DBD Увидел</t>
+  </si>
+  <si>
+    <t>DBD Кошмар на улице Вязов</t>
+  </si>
+  <si>
+    <t>DBD Кожаное лицо</t>
+  </si>
+  <si>
+    <t>DBD О плоти и грязи</t>
+  </si>
+  <si>
+    <t>DBD Колыбельная для тьмы</t>
+  </si>
+  <si>
+    <t>DBD Последний вздох</t>
+  </si>
+  <si>
+    <t>DBD Деревенщина</t>
+  </si>
+  <si>
+    <t>DBD Призрак</t>
+  </si>
+  <si>
+    <t>DBD Охотник</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2431,7 +2494,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q280"/>
+  <dimension ref="A1:Q302"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -10358,7 +10421,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" ref="E252:E279" si="9">A252&amp;"."</f>
+        <f t="shared" ref="E252:E286" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10563,11 +10626,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" ref="J258:J279" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J286" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f t="shared" ref="L258:L279" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L286" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -11254,7 +11317,7 @@
         <v>338</v>
       </c>
       <c r="E280" s="6" t="str">
-        <f>A280&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>279.</v>
       </c>
       <c r="F280" s="19" t="s">
@@ -11267,12 +11330,716 @@
         <v>371</v>
       </c>
       <c r="J280" s="21" t="str">
-        <f>C280&amp;D280&amp;E280&amp;F280&amp;G280</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly279.PQTC.24.03.26</v>
       </c>
       <c r="L280" s="19" t="str">
-        <f>A280&amp;" "&amp;C280&amp;D280&amp;E280&amp;F280&amp;G280&amp;" "&amp;H280</f>
+        <f t="shared" si="11"/>
         <v>279 NtrAntaly279.PQTC.24.03.26 Анталья Ликийские гробницы</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12">
+      <c r="A281" s="5">
+        <v>280</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E281" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>280.</v>
+      </c>
+      <c r="F281" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H281" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="J281" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam280.PQTC.24.03.26</v>
+      </c>
+      <c r="L281" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>280 CupDBDGam280.PQTC.24.03.26 DBD Корни ужаса</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12">
+      <c r="A282" s="5">
+        <v>281</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E282" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>281.</v>
+      </c>
+      <c r="F282" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H282" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="J282" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam281.PQTC.24.03.26</v>
+      </c>
+      <c r="L282" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>281 CupDBDGam281.PQTC.24.03.26 DBD Восход Садако</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12">
+      <c r="A283" s="5">
+        <v>282</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E283" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>282.</v>
+      </c>
+      <c r="F283" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H283" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J283" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam282.PQTC.24.03.26</v>
+      </c>
+      <c r="L283" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>282 CupDBDGam282.PQTC.24.03.26 DBD Resident Evil</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12">
+      <c r="A284" s="5">
+        <v>283</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E284" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>283.</v>
+      </c>
+      <c r="F284" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="J284" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam283.PQTC.24.03.26</v>
+      </c>
+      <c r="L284" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>283 CupDBDGam283.PQTC.24.03.26 DBD Узы родства</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12">
+      <c r="A285" s="5">
+        <v>284</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E285" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>284.</v>
+      </c>
+      <c r="F285" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H285" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="J285" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam284.PQTC.24.03.26</v>
+      </c>
+      <c r="L285" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>284 CupDBDGam284.PQTC.24.03.26 DBD Спуск в преисподнюю</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12">
+      <c r="A286" s="5">
+        <v>285</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E286" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>285.</v>
+      </c>
+      <c r="F286" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="J286" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDBDGam285.PQTC.24.03.26</v>
+      </c>
+      <c r="L286" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>285 CupDBDGam285.PQTC.24.03.26 DBD Сайлент Хилл</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12">
+      <c r="A287" s="5">
+        <v>286</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E287" s="6" t="str">
+        <f>A287&amp;"."</f>
+        <v>286.</v>
+      </c>
+      <c r="F287" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H287" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="J287" s="21" t="str">
+        <f>C287&amp;D287&amp;E287&amp;F287&amp;G287</f>
+        <v>CupDBDGam286.PQTC.24.03.26</v>
+      </c>
+      <c r="L287" s="19" t="str">
+        <f>A287&amp;" "&amp;C287&amp;D287&amp;E287&amp;F287&amp;G287&amp;" "&amp;H287</f>
+        <v>286 CupDBDGam286.PQTC.24.03.26 DBD Цепи ненависти</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12">
+      <c r="A288" s="5">
+        <v>287</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E288" s="6" t="str">
+        <f>A288&amp;"."</f>
+        <v>287.</v>
+      </c>
+      <c r="F288" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H288" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="J288" s="21" t="str">
+        <f>C288&amp;D288&amp;E288&amp;F288&amp;G288</f>
+        <v>CupDBDGam287.PQTC.24.03.26</v>
+      </c>
+      <c r="L288" s="19" t="str">
+        <f>A288&amp;" "&amp;C288&amp;D288&amp;E288&amp;F288&amp;G288&amp;" "&amp;H288</f>
+        <v>287 CupDBDGam287.PQTC.24.03.26 DBD Проклятое наследие</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12">
+      <c r="A289" s="5">
+        <v>288</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E289" s="6" t="str">
+        <f>A289&amp;"."</f>
+        <v>288.</v>
+      </c>
+      <c r="F289" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H289" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="J289" s="21" t="str">
+        <f>C289&amp;D289&amp;E289&amp;F289&amp;G289</f>
+        <v>CupDBDGam288.PQTC.24.03.26</v>
+      </c>
+      <c r="L289" s="19" t="str">
+        <f>A289&amp;" "&amp;C289&amp;D289&amp;E289&amp;F289&amp;G289&amp;" "&amp;H289</f>
+        <v>288 CupDBDGam288.PQTC.24.03.26 DBD Очень странные дела</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12">
+      <c r="A290" s="5">
+        <v>289</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E290" s="6" t="str">
+        <f>A290&amp;"."</f>
+        <v>289.</v>
+      </c>
+      <c r="F290" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J290" s="21" t="str">
+        <f>C290&amp;D290&amp;E290&amp;F290&amp;G290</f>
+        <v>CupDBDGam289.PQTC.24.03.26</v>
+      </c>
+      <c r="L290" s="19" t="str">
+        <f>A290&amp;" "&amp;C290&amp;D290&amp;E290&amp;F290&amp;G290&amp;" "&amp;H290</f>
+        <v>289 CupDBDGam289.PQTC.24.03.26 DBD Конец верных</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12">
+      <c r="A291" s="5">
+        <v>290</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E291" s="6" t="str">
+        <f>A291&amp;"."</f>
+        <v>290.</v>
+      </c>
+      <c r="F291" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H291" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J291" s="21" t="str">
+        <f>C291&amp;D291&amp;E291&amp;F291&amp;G291</f>
+        <v>CupDBDGam290.PQTC.24.03.26</v>
+      </c>
+      <c r="L291" s="19" t="str">
+        <f>A291&amp;" "&amp;C291&amp;D291&amp;E291&amp;F291&amp;G291&amp;" "&amp;H291</f>
+        <v>290 CupDBDGam290.PQTC.24.03.26 DBD Тьма среди нас</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12">
+      <c r="A292" s="5">
+        <v>291</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E292" s="6" t="str">
+        <f>A292&amp;"."</f>
+        <v>291.</v>
+      </c>
+      <c r="F292" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J292" s="21" t="str">
+        <f>C292&amp;D292&amp;E292&amp;F292&amp;G292</f>
+        <v>CupDBDGam291.PQTC.24.03.26</v>
+      </c>
+      <c r="L292" s="19" t="str">
+        <f>A292&amp;" "&amp;C292&amp;D292&amp;E292&amp;F292&amp;G292&amp;" "&amp;H292</f>
+        <v>291 CupDBDGam291.PQTC.24.03.26 DBD Расколотая родословная</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12">
+      <c r="A293" s="5">
+        <v>292</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E293" s="6" t="str">
+        <f>A293&amp;"."</f>
+        <v>292.</v>
+      </c>
+      <c r="F293" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H293" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="J293" s="21" t="str">
+        <f>C293&amp;D293&amp;E293&amp;F293&amp;G293</f>
+        <v>CupDBDGam292.PQTC.24.03.26</v>
+      </c>
+      <c r="L293" s="19" t="str">
+        <f>A293&amp;" "&amp;C293&amp;D293&amp;E293&amp;F293&amp;G293&amp;" "&amp;H293</f>
+        <v>292 CupDBDGam292.PQTC.24.03.26 DBD Занавес</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12">
+      <c r="A294" s="5">
+        <v>293</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E294" s="6" t="str">
+        <f>A294&amp;"."</f>
+        <v>293.</v>
+      </c>
+      <c r="F294" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H294" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="J294" s="21" t="str">
+        <f>C294&amp;D294&amp;E294&amp;F294&amp;G294</f>
+        <v>CupDBDGam293.PQTC.24.03.26</v>
+      </c>
+      <c r="L294" s="19" t="str">
+        <f>A294&amp;" "&amp;C294&amp;D294&amp;E294&amp;F294&amp;G294&amp;" "&amp;H294</f>
+        <v>293 CupDBDGam293.PQTC.24.03.26 DBD Увидел</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12">
+      <c r="A295" s="5">
+        <v>294</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E295" s="6" t="str">
+        <f>A295&amp;"."</f>
+        <v>294.</v>
+      </c>
+      <c r="F295" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H295" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J295" s="21" t="str">
+        <f>C295&amp;D295&amp;E295&amp;F295&amp;G295</f>
+        <v>CupDBDGam294.PQTC.24.03.26</v>
+      </c>
+      <c r="L295" s="19" t="str">
+        <f>A295&amp;" "&amp;C295&amp;D295&amp;E295&amp;F295&amp;G295&amp;" "&amp;H295</f>
+        <v>294 CupDBDGam294.PQTC.24.03.26 DBD Кошмар на улице Вязов</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12">
+      <c r="A296" s="5">
+        <v>295</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E296" s="6" t="str">
+        <f>A296&amp;"."</f>
+        <v>295.</v>
+      </c>
+      <c r="F296" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H296" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="J296" s="21" t="str">
+        <f>C296&amp;D296&amp;E296&amp;F296&amp;G296</f>
+        <v>CupDBDGam295.PQTC.24.03.26</v>
+      </c>
+      <c r="L296" s="19" t="str">
+        <f>A296&amp;" "&amp;C296&amp;D296&amp;E296&amp;F296&amp;G296&amp;" "&amp;H296</f>
+        <v>295 CupDBDGam295.PQTC.24.03.26 DBD Кожаное лицо</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12">
+      <c r="A297" s="5">
+        <v>296</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E297" s="6" t="str">
+        <f>A297&amp;"."</f>
+        <v>296.</v>
+      </c>
+      <c r="F297" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H297" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="J297" s="21" t="str">
+        <f>C297&amp;D297&amp;E297&amp;F297&amp;G297</f>
+        <v>CupDBDGam296.PQTC.24.03.26</v>
+      </c>
+      <c r="L297" s="19" t="str">
+        <f>A297&amp;" "&amp;C297&amp;D297&amp;E297&amp;F297&amp;G297&amp;" "&amp;H297</f>
+        <v>296 CupDBDGam296.PQTC.24.03.26 DBD О плоти и грязи</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12">
+      <c r="A298" s="5">
+        <v>297</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D298" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E298" s="6" t="str">
+        <f>A298&amp;"."</f>
+        <v>297.</v>
+      </c>
+      <c r="F298" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H298" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="J298" s="21" t="str">
+        <f>C298&amp;D298&amp;E298&amp;F298&amp;G298</f>
+        <v>CupDBDGam297.PQTC.24.03.26</v>
+      </c>
+      <c r="L298" s="19" t="str">
+        <f>A298&amp;" "&amp;C298&amp;D298&amp;E298&amp;F298&amp;G298&amp;" "&amp;H298</f>
+        <v>297 CupDBDGam297.PQTC.24.03.26 DBD Колыбельная для тьмы</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12">
+      <c r="A299" s="5">
+        <v>298</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D299" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E299" s="6" t="str">
+        <f>A299&amp;"."</f>
+        <v>298.</v>
+      </c>
+      <c r="F299" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H299" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="J299" s="21" t="str">
+        <f>C299&amp;D299&amp;E299&amp;F299&amp;G299</f>
+        <v>CupDBDGam298.PQTC.24.03.26</v>
+      </c>
+      <c r="L299" s="19" t="str">
+        <f>A299&amp;" "&amp;C299&amp;D299&amp;E299&amp;F299&amp;G299&amp;" "&amp;H299</f>
+        <v>298 CupDBDGam298.PQTC.24.03.26 DBD Последний вздох</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12">
+      <c r="A300" s="5">
+        <v>299</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E300" s="6" t="str">
+        <f>A300&amp;"."</f>
+        <v>299.</v>
+      </c>
+      <c r="F300" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H300" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="J300" s="21" t="str">
+        <f>C300&amp;D300&amp;E300&amp;F300&amp;G300</f>
+        <v>CupDBDGam299.PQTC.24.03.26</v>
+      </c>
+      <c r="L300" s="19" t="str">
+        <f>A300&amp;" "&amp;C300&amp;D300&amp;E300&amp;F300&amp;G300&amp;" "&amp;H300</f>
+        <v>299 CupDBDGam299.PQTC.24.03.26 DBD Деревенщина</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12">
+      <c r="A301" s="5">
+        <v>300</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D301" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E301" s="6" t="str">
+        <f>A301&amp;"."</f>
+        <v>300.</v>
+      </c>
+      <c r="F301" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H301" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J301" s="21" t="str">
+        <f>C301&amp;D301&amp;E301&amp;F301&amp;G301</f>
+        <v>CupDBDGam300.PQTC.24.03.26</v>
+      </c>
+      <c r="L301" s="19" t="str">
+        <f>A301&amp;" "&amp;C301&amp;D301&amp;E301&amp;F301&amp;G301&amp;" "&amp;H301</f>
+        <v>300 CupDBDGam300.PQTC.24.03.26 DBD Призрак</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12">
+      <c r="A302" s="5">
+        <v>301</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E302" s="6" t="str">
+        <f>A302&amp;"."</f>
+        <v>301.</v>
+      </c>
+      <c r="F302" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H302" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="J302" s="21" t="str">
+        <f>C302&amp;D302&amp;E302&amp;F302&amp;G302</f>
+        <v>CupDBDGam301.PQTC.24.03.26</v>
+      </c>
+      <c r="L302" s="19" t="str">
+        <f>A302&amp;" "&amp;C302&amp;D302&amp;E302&amp;F302&amp;G302&amp;" "&amp;H302</f>
+        <v>301 CupDBDGam301.PQTC.24.03.26 DBD Охотник</v>
       </c>
     </row>
   </sheetData>
@@ -11330,127 +12097,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -11458,23 +12225,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -11482,23 +12249,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -11506,39 +12273,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -11546,162 +12313,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="487">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1143,6 +1143,9 @@
     <t>Анталья Аланья</t>
   </si>
   <si>
+    <t>25.03.26</t>
+  </si>
+  <si>
     <t>Анталья Ликийские гробницы</t>
   </si>
   <si>
@@ -1207,6 +1210,15 @@
   </si>
   <si>
     <t>DBD Охотник</t>
+  </si>
+  <si>
+    <t>Анталья минарет Йивли</t>
+  </si>
+  <si>
+    <t>Анталья</t>
+  </si>
+  <si>
+    <t>Анталья башня с часами</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2494,7 +2506,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q302"/>
+  <dimension ref="A1:Q313"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -10421,7 +10433,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" ref="E252:E286" si="9">A252&amp;"."</f>
+        <f t="shared" ref="E252:E302" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10626,11 +10638,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" ref="J258:J286" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J302" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f t="shared" ref="L258:L286" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L302" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -11324,18 +11336,18 @@
         <v>13</v>
       </c>
       <c r="G280" s="8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J280" s="21" t="str">
         <f t="shared" si="10"/>
-        <v>NtrAntaly279.PQTC.24.03.26</v>
+        <v>NtrAntaly279.PQTC.25.03.26</v>
       </c>
       <c r="L280" s="19" t="str">
         <f t="shared" si="11"/>
-        <v>279 NtrAntaly279.PQTC.24.03.26 Анталья Ликийские гробницы</v>
+        <v>279 NtrAntaly279.PQTC.25.03.26 Анталья Ликийские гробницы</v>
       </c>
     </row>
     <row r="281" spans="1:12">
@@ -11359,7 +11371,7 @@
         <v>365</v>
       </c>
       <c r="H281" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J281" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11391,7 +11403,7 @@
         <v>365</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J282" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11423,7 +11435,7 @@
         <v>365</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J283" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11455,7 +11467,7 @@
         <v>365</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J284" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11487,7 +11499,7 @@
         <v>365</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J285" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11519,7 +11531,7 @@
         <v>365</v>
       </c>
       <c r="H286" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J286" s="21" t="str">
         <f t="shared" si="10"/>
@@ -11541,7 +11553,7 @@
         <v>316</v>
       </c>
       <c r="E287" s="6" t="str">
-        <f>A287&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>286.</v>
       </c>
       <c r="F287" s="19" t="s">
@@ -11551,14 +11563,14 @@
         <v>365</v>
       </c>
       <c r="H287" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J287" s="21" t="str">
-        <f>C287&amp;D287&amp;E287&amp;F287&amp;G287</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam286.PQTC.24.03.26</v>
       </c>
       <c r="L287" s="19" t="str">
-        <f>A287&amp;" "&amp;C287&amp;D287&amp;E287&amp;F287&amp;G287&amp;" "&amp;H287</f>
+        <f t="shared" si="11"/>
         <v>286 CupDBDGam286.PQTC.24.03.26 DBD Цепи ненависти</v>
       </c>
     </row>
@@ -11573,7 +11585,7 @@
         <v>316</v>
       </c>
       <c r="E288" s="6" t="str">
-        <f>A288&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>287.</v>
       </c>
       <c r="F288" s="19" t="s">
@@ -11583,14 +11595,14 @@
         <v>365</v>
       </c>
       <c r="H288" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J288" s="21" t="str">
-        <f>C288&amp;D288&amp;E288&amp;F288&amp;G288</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam287.PQTC.24.03.26</v>
       </c>
       <c r="L288" s="19" t="str">
-        <f>A288&amp;" "&amp;C288&amp;D288&amp;E288&amp;F288&amp;G288&amp;" "&amp;H288</f>
+        <f t="shared" si="11"/>
         <v>287 CupDBDGam287.PQTC.24.03.26 DBD Проклятое наследие</v>
       </c>
     </row>
@@ -11605,7 +11617,7 @@
         <v>316</v>
       </c>
       <c r="E289" s="6" t="str">
-        <f>A289&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>288.</v>
       </c>
       <c r="F289" s="19" t="s">
@@ -11618,11 +11630,11 @@
         <v>328</v>
       </c>
       <c r="J289" s="21" t="str">
-        <f>C289&amp;D289&amp;E289&amp;F289&amp;G289</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam288.PQTC.24.03.26</v>
       </c>
       <c r="L289" s="19" t="str">
-        <f>A289&amp;" "&amp;C289&amp;D289&amp;E289&amp;F289&amp;G289&amp;" "&amp;H289</f>
+        <f t="shared" si="11"/>
         <v>288 CupDBDGam288.PQTC.24.03.26 DBD Очень странные дела</v>
       </c>
     </row>
@@ -11637,7 +11649,7 @@
         <v>316</v>
       </c>
       <c r="E290" s="6" t="str">
-        <f>A290&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>289.</v>
       </c>
       <c r="F290" s="19" t="s">
@@ -11647,14 +11659,14 @@
         <v>365</v>
       </c>
       <c r="H290" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J290" s="21" t="str">
-        <f>C290&amp;D290&amp;E290&amp;F290&amp;G290</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam289.PQTC.24.03.26</v>
       </c>
       <c r="L290" s="19" t="str">
-        <f>A290&amp;" "&amp;C290&amp;D290&amp;E290&amp;F290&amp;G290&amp;" "&amp;H290</f>
+        <f t="shared" si="11"/>
         <v>289 CupDBDGam289.PQTC.24.03.26 DBD Конец верных</v>
       </c>
     </row>
@@ -11669,7 +11681,7 @@
         <v>316</v>
       </c>
       <c r="E291" s="6" t="str">
-        <f>A291&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>290.</v>
       </c>
       <c r="F291" s="19" t="s">
@@ -11679,14 +11691,14 @@
         <v>365</v>
       </c>
       <c r="H291" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J291" s="21" t="str">
-        <f>C291&amp;D291&amp;E291&amp;F291&amp;G291</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam290.PQTC.24.03.26</v>
       </c>
       <c r="L291" s="19" t="str">
-        <f>A291&amp;" "&amp;C291&amp;D291&amp;E291&amp;F291&amp;G291&amp;" "&amp;H291</f>
+        <f t="shared" si="11"/>
         <v>290 CupDBDGam290.PQTC.24.03.26 DBD Тьма среди нас</v>
       </c>
     </row>
@@ -11701,7 +11713,7 @@
         <v>316</v>
       </c>
       <c r="E292" s="6" t="str">
-        <f>A292&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>291.</v>
       </c>
       <c r="F292" s="19" t="s">
@@ -11711,14 +11723,14 @@
         <v>365</v>
       </c>
       <c r="H292" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J292" s="21" t="str">
-        <f>C292&amp;D292&amp;E292&amp;F292&amp;G292</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam291.PQTC.24.03.26</v>
       </c>
       <c r="L292" s="19" t="str">
-        <f>A292&amp;" "&amp;C292&amp;D292&amp;E292&amp;F292&amp;G292&amp;" "&amp;H292</f>
+        <f t="shared" si="11"/>
         <v>291 CupDBDGam291.PQTC.24.03.26 DBD Расколотая родословная</v>
       </c>
     </row>
@@ -11733,7 +11745,7 @@
         <v>316</v>
       </c>
       <c r="E293" s="6" t="str">
-        <f>A293&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>292.</v>
       </c>
       <c r="F293" s="19" t="s">
@@ -11743,14 +11755,14 @@
         <v>365</v>
       </c>
       <c r="H293" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J293" s="21" t="str">
-        <f>C293&amp;D293&amp;E293&amp;F293&amp;G293</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam292.PQTC.24.03.26</v>
       </c>
       <c r="L293" s="19" t="str">
-        <f>A293&amp;" "&amp;C293&amp;D293&amp;E293&amp;F293&amp;G293&amp;" "&amp;H293</f>
+        <f t="shared" si="11"/>
         <v>292 CupDBDGam292.PQTC.24.03.26 DBD Занавес</v>
       </c>
     </row>
@@ -11765,7 +11777,7 @@
         <v>316</v>
       </c>
       <c r="E294" s="6" t="str">
-        <f>A294&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>293.</v>
       </c>
       <c r="F294" s="19" t="s">
@@ -11775,14 +11787,14 @@
         <v>365</v>
       </c>
       <c r="H294" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J294" s="21" t="str">
-        <f>C294&amp;D294&amp;E294&amp;F294&amp;G294</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam293.PQTC.24.03.26</v>
       </c>
       <c r="L294" s="19" t="str">
-        <f>A294&amp;" "&amp;C294&amp;D294&amp;E294&amp;F294&amp;G294&amp;" "&amp;H294</f>
+        <f t="shared" si="11"/>
         <v>293 CupDBDGam293.PQTC.24.03.26 DBD Увидел</v>
       </c>
     </row>
@@ -11797,7 +11809,7 @@
         <v>316</v>
       </c>
       <c r="E295" s="6" t="str">
-        <f>A295&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>294.</v>
       </c>
       <c r="F295" s="19" t="s">
@@ -11807,14 +11819,14 @@
         <v>365</v>
       </c>
       <c r="H295" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J295" s="21" t="str">
-        <f>C295&amp;D295&amp;E295&amp;F295&amp;G295</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam294.PQTC.24.03.26</v>
       </c>
       <c r="L295" s="19" t="str">
-        <f>A295&amp;" "&amp;C295&amp;D295&amp;E295&amp;F295&amp;G295&amp;" "&amp;H295</f>
+        <f t="shared" si="11"/>
         <v>294 CupDBDGam294.PQTC.24.03.26 DBD Кошмар на улице Вязов</v>
       </c>
     </row>
@@ -11829,7 +11841,7 @@
         <v>316</v>
       </c>
       <c r="E296" s="6" t="str">
-        <f>A296&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>295.</v>
       </c>
       <c r="F296" s="19" t="s">
@@ -11839,14 +11851,14 @@
         <v>365</v>
       </c>
       <c r="H296" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J296" s="21" t="str">
-        <f>C296&amp;D296&amp;E296&amp;F296&amp;G296</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam295.PQTC.24.03.26</v>
       </c>
       <c r="L296" s="19" t="str">
-        <f>A296&amp;" "&amp;C296&amp;D296&amp;E296&amp;F296&amp;G296&amp;" "&amp;H296</f>
+        <f t="shared" si="11"/>
         <v>295 CupDBDGam295.PQTC.24.03.26 DBD Кожаное лицо</v>
       </c>
     </row>
@@ -11861,7 +11873,7 @@
         <v>316</v>
       </c>
       <c r="E297" s="6" t="str">
-        <f>A297&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>296.</v>
       </c>
       <c r="F297" s="19" t="s">
@@ -11871,14 +11883,14 @@
         <v>365</v>
       </c>
       <c r="H297" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J297" s="21" t="str">
-        <f>C297&amp;D297&amp;E297&amp;F297&amp;G297</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam296.PQTC.24.03.26</v>
       </c>
       <c r="L297" s="19" t="str">
-        <f>A297&amp;" "&amp;C297&amp;D297&amp;E297&amp;F297&amp;G297&amp;" "&amp;H297</f>
+        <f t="shared" si="11"/>
         <v>296 CupDBDGam296.PQTC.24.03.26 DBD О плоти и грязи</v>
       </c>
     </row>
@@ -11893,7 +11905,7 @@
         <v>316</v>
       </c>
       <c r="E298" s="6" t="str">
-        <f>A298&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>297.</v>
       </c>
       <c r="F298" s="19" t="s">
@@ -11903,14 +11915,14 @@
         <v>365</v>
       </c>
       <c r="H298" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J298" s="21" t="str">
-        <f>C298&amp;D298&amp;E298&amp;F298&amp;G298</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam297.PQTC.24.03.26</v>
       </c>
       <c r="L298" s="19" t="str">
-        <f>A298&amp;" "&amp;C298&amp;D298&amp;E298&amp;F298&amp;G298&amp;" "&amp;H298</f>
+        <f t="shared" si="11"/>
         <v>297 CupDBDGam297.PQTC.24.03.26 DBD Колыбельная для тьмы</v>
       </c>
     </row>
@@ -11925,7 +11937,7 @@
         <v>316</v>
       </c>
       <c r="E299" s="6" t="str">
-        <f>A299&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>298.</v>
       </c>
       <c r="F299" s="19" t="s">
@@ -11935,14 +11947,14 @@
         <v>365</v>
       </c>
       <c r="H299" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J299" s="21" t="str">
-        <f>C299&amp;D299&amp;E299&amp;F299&amp;G299</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam298.PQTC.24.03.26</v>
       </c>
       <c r="L299" s="19" t="str">
-        <f>A299&amp;" "&amp;C299&amp;D299&amp;E299&amp;F299&amp;G299&amp;" "&amp;H299</f>
+        <f t="shared" si="11"/>
         <v>298 CupDBDGam298.PQTC.24.03.26 DBD Последний вздох</v>
       </c>
     </row>
@@ -11957,7 +11969,7 @@
         <v>316</v>
       </c>
       <c r="E300" s="6" t="str">
-        <f>A300&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>299.</v>
       </c>
       <c r="F300" s="19" t="s">
@@ -11967,14 +11979,14 @@
         <v>365</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J300" s="21" t="str">
-        <f>C300&amp;D300&amp;E300&amp;F300&amp;G300</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam299.PQTC.24.03.26</v>
       </c>
       <c r="L300" s="19" t="str">
-        <f>A300&amp;" "&amp;C300&amp;D300&amp;E300&amp;F300&amp;G300&amp;" "&amp;H300</f>
+        <f t="shared" si="11"/>
         <v>299 CupDBDGam299.PQTC.24.03.26 DBD Деревенщина</v>
       </c>
     </row>
@@ -11989,7 +12001,7 @@
         <v>316</v>
       </c>
       <c r="E301" s="6" t="str">
-        <f>A301&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>300.</v>
       </c>
       <c r="F301" s="19" t="s">
@@ -11999,14 +12011,14 @@
         <v>365</v>
       </c>
       <c r="H301" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J301" s="21" t="str">
-        <f>C301&amp;D301&amp;E301&amp;F301&amp;G301</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam300.PQTC.24.03.26</v>
       </c>
       <c r="L301" s="19" t="str">
-        <f>A301&amp;" "&amp;C301&amp;D301&amp;E301&amp;F301&amp;G301&amp;" "&amp;H301</f>
+        <f t="shared" si="11"/>
         <v>300 CupDBDGam300.PQTC.24.03.26 DBD Призрак</v>
       </c>
     </row>
@@ -12021,7 +12033,7 @@
         <v>316</v>
       </c>
       <c r="E302" s="6" t="str">
-        <f>A302&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>301.</v>
       </c>
       <c r="F302" s="19" t="s">
@@ -12031,15 +12043,367 @@
         <v>365</v>
       </c>
       <c r="H302" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J302" s="21" t="str">
-        <f>C302&amp;D302&amp;E302&amp;F302&amp;G302</f>
+        <f t="shared" si="10"/>
         <v>CupDBDGam301.PQTC.24.03.26</v>
       </c>
       <c r="L302" s="19" t="str">
-        <f>A302&amp;" "&amp;C302&amp;D302&amp;E302&amp;F302&amp;G302&amp;" "&amp;H302</f>
+        <f t="shared" si="11"/>
         <v>301 CupDBDGam301.PQTC.24.03.26 DBD Охотник</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12">
+      <c r="A303" s="5">
+        <v>302</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E303" s="6" t="str">
+        <f>A303&amp;"."</f>
+        <v>302.</v>
+      </c>
+      <c r="F303" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H303" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J303" s="21" t="str">
+        <f>C303&amp;D303&amp;E303&amp;F303&amp;G303</f>
+        <v>NtrAntaly302.PQTC.25.03.26</v>
+      </c>
+      <c r="L303" s="19" t="str">
+        <f>A303&amp;" "&amp;C303&amp;D303&amp;E303&amp;F303&amp;G303&amp;" "&amp;H303</f>
+        <v>302 NtrAntaly302.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12">
+      <c r="A304" s="5">
+        <v>303</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E304" s="6" t="str">
+        <f>A304&amp;"."</f>
+        <v>303.</v>
+      </c>
+      <c r="F304" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H304" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J304" s="21" t="str">
+        <f>C304&amp;D304&amp;E304&amp;F304&amp;G304</f>
+        <v>NtrAntaly303.PQTC.25.03.26</v>
+      </c>
+      <c r="L304" s="19" t="str">
+        <f>A304&amp;" "&amp;C304&amp;D304&amp;E304&amp;F304&amp;G304&amp;" "&amp;H304</f>
+        <v>303 NtrAntaly303.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12">
+      <c r="A305" s="5">
+        <v>304</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E305" s="6" t="str">
+        <f>A305&amp;"."</f>
+        <v>304.</v>
+      </c>
+      <c r="F305" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H305" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J305" s="21" t="str">
+        <f>C305&amp;D305&amp;E305&amp;F305&amp;G305</f>
+        <v>NtrAntaly304.PQTC.25.03.26</v>
+      </c>
+      <c r="L305" s="19" t="str">
+        <f>A305&amp;" "&amp;C305&amp;D305&amp;E305&amp;F305&amp;G305&amp;" "&amp;H305</f>
+        <v>304 NtrAntaly304.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12">
+      <c r="A306" s="5">
+        <v>305</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E306" s="6" t="str">
+        <f>A306&amp;"."</f>
+        <v>305.</v>
+      </c>
+      <c r="F306" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H306" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J306" s="21" t="str">
+        <f>C306&amp;D306&amp;E306&amp;F306&amp;G306</f>
+        <v>NtrAntaly305.PQTC.25.03.26</v>
+      </c>
+      <c r="L306" s="19" t="str">
+        <f>A306&amp;" "&amp;C306&amp;D306&amp;E306&amp;F306&amp;G306&amp;" "&amp;H306</f>
+        <v>305 NtrAntaly305.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12">
+      <c r="A307" s="5">
+        <v>306</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E307" s="6" t="str">
+        <f>A307&amp;"."</f>
+        <v>306.</v>
+      </c>
+      <c r="F307" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H307" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J307" s="21" t="str">
+        <f>C307&amp;D307&amp;E307&amp;F307&amp;G307</f>
+        <v>NtrAntaly306.PQTC.25.03.26</v>
+      </c>
+      <c r="L307" s="19" t="str">
+        <f>A307&amp;" "&amp;C307&amp;D307&amp;E307&amp;F307&amp;G307&amp;" "&amp;H307</f>
+        <v>306 NtrAntaly306.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12">
+      <c r="A308" s="5">
+        <v>307</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E308" s="6" t="str">
+        <f>A308&amp;"."</f>
+        <v>307.</v>
+      </c>
+      <c r="F308" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H308" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="J308" s="21" t="str">
+        <f>C308&amp;D308&amp;E308&amp;F308&amp;G308</f>
+        <v>NtrAntaly307.PQTC.25.03.26</v>
+      </c>
+      <c r="L308" s="19" t="str">
+        <f>A308&amp;" "&amp;C308&amp;D308&amp;E308&amp;F308&amp;G308&amp;" "&amp;H308</f>
+        <v>307 NtrAntaly307.PQTC.25.03.26 Анталья минарет Йивли</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12">
+      <c r="A309" s="5">
+        <v>308</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E309" s="6" t="str">
+        <f>A309&amp;"."</f>
+        <v>308.</v>
+      </c>
+      <c r="F309" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H309" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J309" s="21" t="str">
+        <f>C309&amp;D309&amp;E309&amp;F309&amp;G309</f>
+        <v>NtrAntaly308.PQTC.25.03.26</v>
+      </c>
+      <c r="L309" s="19" t="str">
+        <f>A309&amp;" "&amp;C309&amp;D309&amp;E309&amp;F309&amp;G309&amp;" "&amp;H309</f>
+        <v>308 NtrAntaly308.PQTC.25.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12">
+      <c r="A310" s="5">
+        <v>309</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E310" s="6" t="str">
+        <f>A310&amp;"."</f>
+        <v>309.</v>
+      </c>
+      <c r="F310" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H310" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J310" s="21" t="str">
+        <f>C310&amp;D310&amp;E310&amp;F310&amp;G310</f>
+        <v>NtrAntaly309.PQTC.25.03.26</v>
+      </c>
+      <c r="L310" s="19" t="str">
+        <f>A310&amp;" "&amp;C310&amp;D310&amp;E310&amp;F310&amp;G310&amp;" "&amp;H310</f>
+        <v>309 NtrAntaly309.PQTC.25.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12">
+      <c r="A311" s="5">
+        <v>310</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E311" s="6" t="str">
+        <f>A311&amp;"."</f>
+        <v>310.</v>
+      </c>
+      <c r="F311" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H311" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J311" s="21" t="str">
+        <f>C311&amp;D311&amp;E311&amp;F311&amp;G311</f>
+        <v>NtrAntaly310.PQTC.25.03.26</v>
+      </c>
+      <c r="L311" s="19" t="str">
+        <f>A311&amp;" "&amp;C311&amp;D311&amp;E311&amp;F311&amp;G311&amp;" "&amp;H311</f>
+        <v>310 NtrAntaly310.PQTC.25.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12">
+      <c r="A312" s="5">
+        <v>311</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E312" s="6" t="str">
+        <f>A312&amp;"."</f>
+        <v>311.</v>
+      </c>
+      <c r="F312" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H312" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J312" s="21" t="str">
+        <f>C312&amp;D312&amp;E312&amp;F312&amp;G312</f>
+        <v>NtrAntaly311.PQTC.25.03.26</v>
+      </c>
+      <c r="L312" s="19" t="str">
+        <f>A312&amp;" "&amp;C312&amp;D312&amp;E312&amp;F312&amp;G312&amp;" "&amp;H312</f>
+        <v>311 NtrAntaly311.PQTC.25.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12">
+      <c r="A313" s="5">
+        <v>312</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E313" s="6" t="str">
+        <f>A313&amp;"."</f>
+        <v>312.</v>
+      </c>
+      <c r="F313" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H313" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="J313" s="21" t="str">
+        <f>C313&amp;D313&amp;E313&amp;F313&amp;G313</f>
+        <v>NtrAntaly312.PQTC.25.03.26</v>
+      </c>
+      <c r="L313" s="19" t="str">
+        <f>A313&amp;" "&amp;C313&amp;D313&amp;E313&amp;F313&amp;G313&amp;" "&amp;H313</f>
+        <v>312 NtrAntaly312.PQTC.25.03.26 Анталья башня с часами</v>
       </c>
     </row>
   </sheetData>
@@ -12097,127 +12461,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -12225,23 +12589,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -12249,23 +12613,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -12273,39 +12637,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -12313,162 +12677,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="501">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1219,6 +1219,48 @@
   </si>
   <si>
     <t>Анталья башня с часами</t>
+  </si>
+  <si>
+    <t>DontSt</t>
+  </si>
+  <si>
+    <t>26.03.26</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_2</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_3</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_4</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_5</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_6</t>
+  </si>
+  <si>
+    <t>Обложка_Уилсон_7</t>
+  </si>
+  <si>
+    <t>Обложка_Максвелл</t>
+  </si>
+  <si>
+    <t>Обложка_Verdant</t>
+  </si>
+  <si>
+    <t>Обложка_Персонажи_1</t>
+  </si>
+  <si>
+    <t>Обложка_Персонажи_2</t>
+  </si>
+  <si>
+    <t>27.03.26</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2506,7 +2548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q313"/>
+  <dimension ref="A1:Q327"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -10433,7 +10475,7 @@
         <v>338</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" ref="E252:E302" si="9">A252&amp;"."</f>
+        <f t="shared" ref="E252:E315" si="9">A252&amp;"."</f>
         <v>251.</v>
       </c>
       <c r="F252" s="19" t="s">
@@ -10638,11 +10680,11 @@
         <v>363</v>
       </c>
       <c r="J258" s="21" t="str">
-        <f t="shared" ref="J258:J302" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
+        <f t="shared" ref="J258:J321" si="10">C258&amp;D258&amp;E258&amp;F258&amp;G258</f>
         <v>NtrAntaly257.PQTC.21.03.26</v>
       </c>
       <c r="L258" s="19" t="str">
-        <f t="shared" ref="L258:L302" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
+        <f t="shared" ref="L258:L321" si="11">A258&amp;" "&amp;C258&amp;D258&amp;E258&amp;F258&amp;G258&amp;" "&amp;H258</f>
         <v>257 NtrAntaly257.PQTC.21.03.26 Анталья храм Аполлона Сиде</v>
       </c>
     </row>
@@ -12065,7 +12107,7 @@
         <v>338</v>
       </c>
       <c r="E303" s="6" t="str">
-        <f>A303&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>302.</v>
       </c>
       <c r="F303" s="19" t="s">
@@ -12078,11 +12120,11 @@
         <v>394</v>
       </c>
       <c r="J303" s="21" t="str">
-        <f>C303&amp;D303&amp;E303&amp;F303&amp;G303</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly302.PQTC.25.03.26</v>
       </c>
       <c r="L303" s="19" t="str">
-        <f>A303&amp;" "&amp;C303&amp;D303&amp;E303&amp;F303&amp;G303&amp;" "&amp;H303</f>
+        <f t="shared" si="11"/>
         <v>302 NtrAntaly302.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12097,7 +12139,7 @@
         <v>338</v>
       </c>
       <c r="E304" s="6" t="str">
-        <f>A304&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>303.</v>
       </c>
       <c r="F304" s="19" t="s">
@@ -12110,11 +12152,11 @@
         <v>394</v>
       </c>
       <c r="J304" s="21" t="str">
-        <f>C304&amp;D304&amp;E304&amp;F304&amp;G304</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly303.PQTC.25.03.26</v>
       </c>
       <c r="L304" s="19" t="str">
-        <f>A304&amp;" "&amp;C304&amp;D304&amp;E304&amp;F304&amp;G304&amp;" "&amp;H304</f>
+        <f t="shared" si="11"/>
         <v>303 NtrAntaly303.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12129,7 +12171,7 @@
         <v>338</v>
       </c>
       <c r="E305" s="6" t="str">
-        <f>A305&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>304.</v>
       </c>
       <c r="F305" s="19" t="s">
@@ -12142,11 +12184,11 @@
         <v>394</v>
       </c>
       <c r="J305" s="21" t="str">
-        <f>C305&amp;D305&amp;E305&amp;F305&amp;G305</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly304.PQTC.25.03.26</v>
       </c>
       <c r="L305" s="19" t="str">
-        <f>A305&amp;" "&amp;C305&amp;D305&amp;E305&amp;F305&amp;G305&amp;" "&amp;H305</f>
+        <f t="shared" si="11"/>
         <v>304 NtrAntaly304.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12161,7 +12203,7 @@
         <v>338</v>
       </c>
       <c r="E306" s="6" t="str">
-        <f>A306&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>305.</v>
       </c>
       <c r="F306" s="19" t="s">
@@ -12174,11 +12216,11 @@
         <v>394</v>
       </c>
       <c r="J306" s="21" t="str">
-        <f>C306&amp;D306&amp;E306&amp;F306&amp;G306</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly305.PQTC.25.03.26</v>
       </c>
       <c r="L306" s="19" t="str">
-        <f>A306&amp;" "&amp;C306&amp;D306&amp;E306&amp;F306&amp;G306&amp;" "&amp;H306</f>
+        <f t="shared" si="11"/>
         <v>305 NtrAntaly305.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12193,7 +12235,7 @@
         <v>338</v>
       </c>
       <c r="E307" s="6" t="str">
-        <f>A307&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>306.</v>
       </c>
       <c r="F307" s="19" t="s">
@@ -12206,11 +12248,11 @@
         <v>394</v>
       </c>
       <c r="J307" s="21" t="str">
-        <f>C307&amp;D307&amp;E307&amp;F307&amp;G307</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly306.PQTC.25.03.26</v>
       </c>
       <c r="L307" s="19" t="str">
-        <f>A307&amp;" "&amp;C307&amp;D307&amp;E307&amp;F307&amp;G307&amp;" "&amp;H307</f>
+        <f t="shared" si="11"/>
         <v>306 NtrAntaly306.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12225,7 +12267,7 @@
         <v>338</v>
       </c>
       <c r="E308" s="6" t="str">
-        <f>A308&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>307.</v>
       </c>
       <c r="F308" s="19" t="s">
@@ -12238,11 +12280,11 @@
         <v>394</v>
       </c>
       <c r="J308" s="21" t="str">
-        <f>C308&amp;D308&amp;E308&amp;F308&amp;G308</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly307.PQTC.25.03.26</v>
       </c>
       <c r="L308" s="19" t="str">
-        <f>A308&amp;" "&amp;C308&amp;D308&amp;E308&amp;F308&amp;G308&amp;" "&amp;H308</f>
+        <f t="shared" si="11"/>
         <v>307 NtrAntaly307.PQTC.25.03.26 Анталья минарет Йивли</v>
       </c>
     </row>
@@ -12257,7 +12299,7 @@
         <v>338</v>
       </c>
       <c r="E309" s="6" t="str">
-        <f>A309&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>308.</v>
       </c>
       <c r="F309" s="19" t="s">
@@ -12270,11 +12312,11 @@
         <v>395</v>
       </c>
       <c r="J309" s="21" t="str">
-        <f>C309&amp;D309&amp;E309&amp;F309&amp;G309</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly308.PQTC.25.03.26</v>
       </c>
       <c r="L309" s="19" t="str">
-        <f>A309&amp;" "&amp;C309&amp;D309&amp;E309&amp;F309&amp;G309&amp;" "&amp;H309</f>
+        <f t="shared" si="11"/>
         <v>308 NtrAntaly308.PQTC.25.03.26 Анталья</v>
       </c>
     </row>
@@ -12289,7 +12331,7 @@
         <v>338</v>
       </c>
       <c r="E310" s="6" t="str">
-        <f>A310&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>309.</v>
       </c>
       <c r="F310" s="19" t="s">
@@ -12302,11 +12344,11 @@
         <v>395</v>
       </c>
       <c r="J310" s="21" t="str">
-        <f>C310&amp;D310&amp;E310&amp;F310&amp;G310</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly309.PQTC.25.03.26</v>
       </c>
       <c r="L310" s="19" t="str">
-        <f>A310&amp;" "&amp;C310&amp;D310&amp;E310&amp;F310&amp;G310&amp;" "&amp;H310</f>
+        <f t="shared" si="11"/>
         <v>309 NtrAntaly309.PQTC.25.03.26 Анталья</v>
       </c>
     </row>
@@ -12321,7 +12363,7 @@
         <v>338</v>
       </c>
       <c r="E311" s="6" t="str">
-        <f>A311&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>310.</v>
       </c>
       <c r="F311" s="19" t="s">
@@ -12334,11 +12376,11 @@
         <v>395</v>
       </c>
       <c r="J311" s="21" t="str">
-        <f>C311&amp;D311&amp;E311&amp;F311&amp;G311</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly310.PQTC.25.03.26</v>
       </c>
       <c r="L311" s="19" t="str">
-        <f>A311&amp;" "&amp;C311&amp;D311&amp;E311&amp;F311&amp;G311&amp;" "&amp;H311</f>
+        <f t="shared" si="11"/>
         <v>310 NtrAntaly310.PQTC.25.03.26 Анталья</v>
       </c>
     </row>
@@ -12353,7 +12395,7 @@
         <v>338</v>
       </c>
       <c r="E312" s="6" t="str">
-        <f>A312&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>311.</v>
       </c>
       <c r="F312" s="19" t="s">
@@ -12366,11 +12408,11 @@
         <v>395</v>
       </c>
       <c r="J312" s="21" t="str">
-        <f>C312&amp;D312&amp;E312&amp;F312&amp;G312</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly311.PQTC.25.03.26</v>
       </c>
       <c r="L312" s="19" t="str">
-        <f>A312&amp;" "&amp;C312&amp;D312&amp;E312&amp;F312&amp;G312&amp;" "&amp;H312</f>
+        <f t="shared" si="11"/>
         <v>311 NtrAntaly311.PQTC.25.03.26 Анталья</v>
       </c>
     </row>
@@ -12385,7 +12427,7 @@
         <v>338</v>
       </c>
       <c r="E313" s="6" t="str">
-        <f>A313&amp;"."</f>
+        <f t="shared" si="9"/>
         <v>312.</v>
       </c>
       <c r="F313" s="19" t="s">
@@ -12398,12 +12440,460 @@
         <v>396</v>
       </c>
       <c r="J313" s="21" t="str">
-        <f>C313&amp;D313&amp;E313&amp;F313&amp;G313</f>
+        <f t="shared" si="10"/>
         <v>NtrAntaly312.PQTC.25.03.26</v>
       </c>
       <c r="L313" s="19" t="str">
-        <f>A313&amp;" "&amp;C313&amp;D313&amp;E313&amp;F313&amp;G313&amp;" "&amp;H313</f>
+        <f t="shared" si="11"/>
         <v>312 NtrAntaly312.PQTC.25.03.26 Анталья башня с часами</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12">
+      <c r="A314" s="5">
+        <v>313</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E314" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>313.</v>
+      </c>
+      <c r="F314" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H314" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="J314" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt313.PQTC.26.03.26</v>
+      </c>
+      <c r="L314" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>313 CupDontSt313.PQTC.26.03.26 Обложка_Уилсон</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12">
+      <c r="A315" s="5">
+        <v>314</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E315" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>314.</v>
+      </c>
+      <c r="F315" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H315" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="J315" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt314.PQTC.26.03.26</v>
+      </c>
+      <c r="L315" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>314 CupDontSt314.PQTC.26.03.26 Обложка_Уилсон_2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12">
+      <c r="A316" s="5">
+        <v>315</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E316" s="6" t="str">
+        <f t="shared" ref="E316:E324" si="12">A316&amp;"."</f>
+        <v>315.</v>
+      </c>
+      <c r="F316" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H316" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J316" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt315.PQTC.26.03.26</v>
+      </c>
+      <c r="L316" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>315 CupDontSt315.PQTC.26.03.26 Обложка_Уилсон_3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12">
+      <c r="A317" s="5">
+        <v>316</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E317" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>316.</v>
+      </c>
+      <c r="F317" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H317" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="J317" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt316.PQTC.26.03.26</v>
+      </c>
+      <c r="L317" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>316 CupDontSt316.PQTC.26.03.26 Обложка_Уилсон_4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12">
+      <c r="A318" s="5">
+        <v>317</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E318" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>317.</v>
+      </c>
+      <c r="F318" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G318" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H318" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="J318" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt317.PQTC.26.03.26</v>
+      </c>
+      <c r="L318" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>317 CupDontSt317.PQTC.26.03.26 Обложка_Уилсон_5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12">
+      <c r="A319" s="5">
+        <v>318</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E319" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>318.</v>
+      </c>
+      <c r="F319" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G319" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H319" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="J319" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt318.PQTC.26.03.26</v>
+      </c>
+      <c r="L319" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>318 CupDontSt318.PQTC.26.03.26 Обложка_Уилсон_6</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12">
+      <c r="A320" s="5">
+        <v>319</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E320" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>319.</v>
+      </c>
+      <c r="F320" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G320" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H320" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="J320" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt319.PQTC.26.03.26</v>
+      </c>
+      <c r="L320" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>319 CupDontSt319.PQTC.26.03.26 Обложка_Уилсон_7</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12">
+      <c r="A321" s="5">
+        <v>320</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E321" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>320.</v>
+      </c>
+      <c r="F321" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G321" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H321" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="J321" s="21" t="str">
+        <f t="shared" si="10"/>
+        <v>CupDontSt320.PQTC.26.03.26</v>
+      </c>
+      <c r="L321" s="19" t="str">
+        <f t="shared" si="11"/>
+        <v>320 CupDontSt320.PQTC.26.03.26 Обложка_Максвелл</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12">
+      <c r="A322" s="5">
+        <v>321</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D322" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E322" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>321.</v>
+      </c>
+      <c r="F322" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G322" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H322" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="J322" s="21" t="str">
+        <f>C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <v>CupDontSt321.PQTC.26.03.26</v>
+      </c>
+      <c r="L322" s="19" t="str">
+        <f>A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12">
+      <c r="A323" s="5">
+        <v>322</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E323" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>322.</v>
+      </c>
+      <c r="F323" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G323" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H323" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="J323" s="21" t="str">
+        <f>C323&amp;D323&amp;E323&amp;F323&amp;G323</f>
+        <v>CupDontSt322.PQTC.26.03.26</v>
+      </c>
+      <c r="L323" s="19" t="str">
+        <f>A323&amp;" "&amp;C323&amp;D323&amp;E323&amp;F323&amp;G323&amp;" "&amp;H323</f>
+        <v>322 CupDontSt322.PQTC.26.03.26 Обложка_Персонажи_1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12">
+      <c r="A324" s="5">
+        <v>323</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E324" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>323.</v>
+      </c>
+      <c r="F324" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G324" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H324" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="J324" s="21" t="str">
+        <f>C324&amp;D324&amp;E324&amp;F324&amp;G324</f>
+        <v>CupDontSt323.PQTC.26.03.26</v>
+      </c>
+      <c r="L324" s="19" t="str">
+        <f>A324&amp;" "&amp;C324&amp;D324&amp;E324&amp;F324&amp;G324&amp;" "&amp;H324</f>
+        <v>323 CupDontSt323.PQTC.26.03.26 Обложка_Персонажи_2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12">
+      <c r="A325" s="5">
+        <v>324</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E325" s="6" t="str">
+        <f>A325&amp;"."</f>
+        <v>324.</v>
+      </c>
+      <c r="F325" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G325" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H325" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J325" s="21" t="str">
+        <f>C325&amp;D325&amp;E325&amp;F325&amp;G325</f>
+        <v>NtrAntaly324.PQTC.27.03.26</v>
+      </c>
+      <c r="L325" s="19" t="str">
+        <f>A325&amp;" "&amp;C325&amp;D325&amp;E325&amp;F325&amp;G325&amp;" "&amp;H325</f>
+        <v>324 NtrAntaly324.PQTC.27.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12">
+      <c r="A326" s="5">
+        <v>325</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E326" s="6" t="str">
+        <f>A326&amp;"."</f>
+        <v>325.</v>
+      </c>
+      <c r="F326" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G326" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H326" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J326" s="21" t="str">
+        <f>C326&amp;D326&amp;E326&amp;F326&amp;G326</f>
+        <v>NtrAntaly325.PQTC.27.03.26</v>
+      </c>
+      <c r="L326" s="19" t="str">
+        <f>A326&amp;" "&amp;C326&amp;D326&amp;E326&amp;F326&amp;G326&amp;" "&amp;H326</f>
+        <v>325 NtrAntaly325.PQTC.27.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12">
+      <c r="A327" s="5">
+        <v>326</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E327" s="6" t="str">
+        <f>A327&amp;"."</f>
+        <v>326.</v>
+      </c>
+      <c r="F327" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G327" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H327" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J327" s="21" t="str">
+        <f>C327&amp;D327&amp;E327&amp;F327&amp;G327</f>
+        <v>NtrAntaly326.PQTC.27.03.26</v>
+      </c>
+      <c r="L327" s="19" t="str">
+        <f>A327&amp;" "&amp;C327&amp;D327&amp;E327&amp;F327&amp;G327&amp;" "&amp;H327</f>
+        <v>326 NtrAntaly326.PQTC.27.03.26 Анталья</v>
       </c>
     </row>
   </sheetData>
@@ -12461,127 +12951,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -12589,23 +13079,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -12613,23 +13103,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -12637,39 +13127,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -12677,162 +13167,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="516">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1261,6 +1261,51 @@
   </si>
   <si>
     <t>27.03.26</t>
+  </si>
+  <si>
+    <t>Анталья горы</t>
+  </si>
+  <si>
+    <t>Анталья канатная дорога</t>
+  </si>
+  <si>
+    <t>Анталья амфитеатр Сиде</t>
+  </si>
+  <si>
+    <t>Анталья Дом-музей Ататюрка</t>
+  </si>
+  <si>
+    <t>Анталья Археологический музей</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Уилсон</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Венди</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Венди_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу_3</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Вуди</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Персонажи</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Персонажи_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Циклоп-олень</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2548,7 +2593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q327"/>
+  <dimension ref="A1:Q345"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
@@ -12523,7 +12568,7 @@
         <v>397</v>
       </c>
       <c r="E316" s="6" t="str">
-        <f t="shared" ref="E316:E324" si="12">A316&amp;"."</f>
+        <f t="shared" ref="E316:E335" si="12">A316&amp;"."</f>
         <v>315.</v>
       </c>
       <c r="F316" s="19" t="s">
@@ -12728,11 +12773,11 @@
         <v>407</v>
       </c>
       <c r="J322" s="21" t="str">
-        <f>C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <f t="shared" ref="J322:J335" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
         <v>CupDontSt321.PQTC.26.03.26</v>
       </c>
       <c r="L322" s="19" t="str">
-        <f>A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <f t="shared" ref="L322:L335" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
         <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
       </c>
     </row>
@@ -12760,11 +12805,11 @@
         <v>408</v>
       </c>
       <c r="J323" s="21" t="str">
-        <f>C323&amp;D323&amp;E323&amp;F323&amp;G323</f>
+        <f t="shared" si="13"/>
         <v>CupDontSt322.PQTC.26.03.26</v>
       </c>
       <c r="L323" s="19" t="str">
-        <f>A323&amp;" "&amp;C323&amp;D323&amp;E323&amp;F323&amp;G323&amp;" "&amp;H323</f>
+        <f t="shared" si="14"/>
         <v>322 CupDontSt322.PQTC.26.03.26 Обложка_Персонажи_1</v>
       </c>
     </row>
@@ -12792,11 +12837,11 @@
         <v>409</v>
       </c>
       <c r="J324" s="21" t="str">
-        <f>C324&amp;D324&amp;E324&amp;F324&amp;G324</f>
+        <f t="shared" si="13"/>
         <v>CupDontSt323.PQTC.26.03.26</v>
       </c>
       <c r="L324" s="19" t="str">
-        <f>A324&amp;" "&amp;C324&amp;D324&amp;E324&amp;F324&amp;G324&amp;" "&amp;H324</f>
+        <f t="shared" si="14"/>
         <v>323 CupDontSt323.PQTC.26.03.26 Обложка_Персонажи_2</v>
       </c>
     </row>
@@ -12811,7 +12856,7 @@
         <v>338</v>
       </c>
       <c r="E325" s="6" t="str">
-        <f>A325&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>324.</v>
       </c>
       <c r="F325" s="19" t="s">
@@ -12824,11 +12869,11 @@
         <v>395</v>
       </c>
       <c r="J325" s="21" t="str">
-        <f>C325&amp;D325&amp;E325&amp;F325&amp;G325</f>
+        <f t="shared" si="13"/>
         <v>NtrAntaly324.PQTC.27.03.26</v>
       </c>
       <c r="L325" s="19" t="str">
-        <f>A325&amp;" "&amp;C325&amp;D325&amp;E325&amp;F325&amp;G325&amp;" "&amp;H325</f>
+        <f t="shared" si="14"/>
         <v>324 NtrAntaly324.PQTC.27.03.26 Анталья</v>
       </c>
     </row>
@@ -12843,7 +12888,7 @@
         <v>338</v>
       </c>
       <c r="E326" s="6" t="str">
-        <f>A326&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>325.</v>
       </c>
       <c r="F326" s="19" t="s">
@@ -12856,11 +12901,11 @@
         <v>395</v>
       </c>
       <c r="J326" s="21" t="str">
-        <f>C326&amp;D326&amp;E326&amp;F326&amp;G326</f>
+        <f t="shared" si="13"/>
         <v>NtrAntaly325.PQTC.27.03.26</v>
       </c>
       <c r="L326" s="19" t="str">
-        <f>A326&amp;" "&amp;C326&amp;D326&amp;E326&amp;F326&amp;G326&amp;" "&amp;H326</f>
+        <f t="shared" si="14"/>
         <v>325 NtrAntaly325.PQTC.27.03.26 Анталья</v>
       </c>
     </row>
@@ -12875,7 +12920,7 @@
         <v>338</v>
       </c>
       <c r="E327" s="6" t="str">
-        <f>A327&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>326.</v>
       </c>
       <c r="F327" s="19" t="s">
@@ -12888,12 +12933,588 @@
         <v>395</v>
       </c>
       <c r="J327" s="21" t="str">
-        <f>C327&amp;D327&amp;E327&amp;F327&amp;G327</f>
+        <f t="shared" si="13"/>
         <v>NtrAntaly326.PQTC.27.03.26</v>
       </c>
       <c r="L327" s="19" t="str">
-        <f>A327&amp;" "&amp;C327&amp;D327&amp;E327&amp;F327&amp;G327&amp;" "&amp;H327</f>
+        <f t="shared" si="14"/>
         <v>326 NtrAntaly326.PQTC.27.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12">
+      <c r="A328" s="5">
+        <v>327</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E328" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>327.</v>
+      </c>
+      <c r="F328" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G328" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H328" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J328" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly327.PQTC.27.03.26</v>
+      </c>
+      <c r="L328" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>327 NtrAntaly327.PQTC.27.03.26 Анталья</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12">
+      <c r="A329" s="5">
+        <v>328</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D329" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E329" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>328.</v>
+      </c>
+      <c r="F329" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G329" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H329" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="J329" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly328.PQTC.27.03.26</v>
+      </c>
+      <c r="L329" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>328 NtrAntaly328.PQTC.27.03.26 Анталья горы</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12">
+      <c r="A330" s="5">
+        <v>329</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D330" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E330" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>329.</v>
+      </c>
+      <c r="F330" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G330" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H330" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="J330" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly329.PQTC.27.03.26</v>
+      </c>
+      <c r="L330" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>329 NtrAntaly329.PQTC.27.03.26 Анталья канатная дорога</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12">
+      <c r="A331" s="5">
+        <v>330</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D331" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E331" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>330.</v>
+      </c>
+      <c r="F331" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G331" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H331" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="J331" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly330.PQTC.27.03.26</v>
+      </c>
+      <c r="L331" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>330 NtrAntaly330.PQTC.27.03.26 Анталья канатная дорога</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12">
+      <c r="A332" s="5">
+        <v>331</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D332" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E332" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>331.</v>
+      </c>
+      <c r="F332" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G332" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H332" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="J332" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly331.PQTC.27.03.26</v>
+      </c>
+      <c r="L332" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>331 NtrAntaly331.PQTC.27.03.26 Анталья амфитеатр Сиде</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12">
+      <c r="A333" s="5">
+        <v>332</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E333" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>332.</v>
+      </c>
+      <c r="F333" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G333" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H333" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="J333" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly332.PQTC.27.03.26</v>
+      </c>
+      <c r="L333" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>332 NtrAntaly332.PQTC.27.03.26 Анталья Аспендос</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12">
+      <c r="A334" s="5">
+        <v>333</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E334" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>333.</v>
+      </c>
+      <c r="F334" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G334" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H334" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="J334" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly333.PQTC.27.03.26</v>
+      </c>
+      <c r="L334" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>333 NtrAntaly333.PQTC.27.03.26 Анталья Дом-музей Ататюрка</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12">
+      <c r="A335" s="5">
+        <v>334</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E335" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>334.</v>
+      </c>
+      <c r="F335" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G335" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H335" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J335" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>NtrAntaly334.PQTC.27.03.26</v>
+      </c>
+      <c r="L335" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>334 NtrAntaly334.PQTC.27.03.26 Анталья Археологический музей</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12">
+      <c r="A336" s="5">
+        <v>335</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E336" s="6" t="str">
+        <f>A336&amp;"."</f>
+        <v>335.</v>
+      </c>
+      <c r="F336" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G336" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H336" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="J336" s="21" t="str">
+        <f>C336&amp;D336&amp;E336&amp;F336&amp;G336</f>
+        <v>NtrDontSt335.PQTC.27.03.26</v>
+      </c>
+      <c r="L336" s="19" t="str">
+        <f>A336&amp;" "&amp;C336&amp;D336&amp;E336&amp;F336&amp;G336&amp;" "&amp;H336</f>
+        <v>335 NtrDontSt335.PQTC.27.03.26 Dont_Starve_Уилсон</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12">
+      <c r="A337" s="5">
+        <v>336</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D337" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E337" s="6" t="str">
+        <f>A337&amp;"."</f>
+        <v>336.</v>
+      </c>
+      <c r="F337" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G337" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H337" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="J337" s="21" t="str">
+        <f>C337&amp;D337&amp;E337&amp;F337&amp;G337</f>
+        <v>NtrDontSt336.PQTC.27.03.26</v>
+      </c>
+      <c r="L337" s="19" t="str">
+        <f>A337&amp;" "&amp;C337&amp;D337&amp;E337&amp;F337&amp;G337&amp;" "&amp;H337</f>
+        <v>336 NtrDontSt336.PQTC.27.03.26 Dont_Starve_Венди</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12">
+      <c r="A338" s="5">
+        <v>337</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D338" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E338" s="6" t="str">
+        <f>A338&amp;"."</f>
+        <v>337.</v>
+      </c>
+      <c r="F338" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G338" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H338" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="J338" s="21" t="str">
+        <f>C338&amp;D338&amp;E338&amp;F338&amp;G338</f>
+        <v>NtrDontSt337.PQTC.27.03.26</v>
+      </c>
+      <c r="L338" s="19" t="str">
+        <f>A338&amp;" "&amp;C338&amp;D338&amp;E338&amp;F338&amp;G338&amp;" "&amp;H338</f>
+        <v>337 NtrDontSt337.PQTC.27.03.26 Dont_Starve_Венди_2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12">
+      <c r="A339" s="5">
+        <v>338</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D339" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E339" s="6" t="str">
+        <f>A339&amp;"."</f>
+        <v>338.</v>
+      </c>
+      <c r="F339" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G339" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H339" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="J339" s="21" t="str">
+        <f>C339&amp;D339&amp;E339&amp;F339&amp;G339</f>
+        <v>NtrDontSt338.PQTC.27.03.26</v>
+      </c>
+      <c r="L339" s="19" t="str">
+        <f>A339&amp;" "&amp;C339&amp;D339&amp;E339&amp;F339&amp;G339&amp;" "&amp;H339</f>
+        <v>338 NtrDontSt338.PQTC.27.03.26 Dont_Starve_ Уиллоу</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12">
+      <c r="A340" s="5">
+        <v>339</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E340" s="6" t="str">
+        <f>A340&amp;"."</f>
+        <v>339.</v>
+      </c>
+      <c r="F340" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G340" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H340" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="J340" s="21" t="str">
+        <f>C340&amp;D340&amp;E340&amp;F340&amp;G340</f>
+        <v>NtrDontSt339.PQTC.27.03.26</v>
+      </c>
+      <c r="L340" s="19" t="str">
+        <f>A340&amp;" "&amp;C340&amp;D340&amp;E340&amp;F340&amp;G340&amp;" "&amp;H340</f>
+        <v>339 NtrDontSt339.PQTC.27.03.26 Dont_Starve_ Уиллоу_2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12">
+      <c r="A341" s="5">
+        <v>340</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D341" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E341" s="6" t="str">
+        <f>A341&amp;"."</f>
+        <v>340.</v>
+      </c>
+      <c r="F341" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G341" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H341" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="J341" s="21" t="str">
+        <f>C341&amp;D341&amp;E341&amp;F341&amp;G341</f>
+        <v>NtrDontSt340.PQTC.27.03.26</v>
+      </c>
+      <c r="L341" s="19" t="str">
+        <f>A341&amp;" "&amp;C341&amp;D341&amp;E341&amp;F341&amp;G341&amp;" "&amp;H341</f>
+        <v>340 NtrDontSt340.PQTC.27.03.26 Dont_Starve_ Уиллоу_3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12">
+      <c r="A342" s="5">
+        <v>341</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E342" s="6" t="str">
+        <f>A342&amp;"."</f>
+        <v>341.</v>
+      </c>
+      <c r="F342" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G342" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H342" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="J342" s="21" t="str">
+        <f>C342&amp;D342&amp;E342&amp;F342&amp;G342</f>
+        <v>NtrDontSt341.PQTC.27.03.26</v>
+      </c>
+      <c r="L342" s="19" t="str">
+        <f>A342&amp;" "&amp;C342&amp;D342&amp;E342&amp;F342&amp;G342&amp;" "&amp;H342</f>
+        <v>341 NtrDontSt341.PQTC.27.03.26 Dont_Starve_Вуди</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12">
+      <c r="A343" s="5">
+        <v>342</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E343" s="6" t="str">
+        <f>A343&amp;"."</f>
+        <v>342.</v>
+      </c>
+      <c r="F343" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G343" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H343" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="J343" s="21" t="str">
+        <f>C343&amp;D343&amp;E343&amp;F343&amp;G343</f>
+        <v>NtrDontSt342.PQTC.27.03.26</v>
+      </c>
+      <c r="L343" s="19" t="str">
+        <f>A343&amp;" "&amp;C343&amp;D343&amp;E343&amp;F343&amp;G343&amp;" "&amp;H343</f>
+        <v>342 NtrDontSt342.PQTC.27.03.26 Dont_Starve_Персонажи</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12">
+      <c r="A344" s="5">
+        <v>343</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E344" s="6" t="str">
+        <f>A344&amp;"."</f>
+        <v>343.</v>
+      </c>
+      <c r="F344" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G344" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H344" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="J344" s="21" t="str">
+        <f>C344&amp;D344&amp;E344&amp;F344&amp;G344</f>
+        <v>NtrDontSt343.PQTC.27.03.26</v>
+      </c>
+      <c r="L344" s="19" t="str">
+        <f>A344&amp;" "&amp;C344&amp;D344&amp;E344&amp;F344&amp;G344&amp;" "&amp;H344</f>
+        <v>343 NtrDontSt343.PQTC.27.03.26 Dont_Starve_Персонажи_2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12">
+      <c r="A345" s="5">
+        <v>344</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D345" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="E345" s="6" t="str">
+        <f>A345&amp;"."</f>
+        <v>344.</v>
+      </c>
+      <c r="F345" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G345" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="H345" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="J345" s="21" t="str">
+        <f>C345&amp;D345&amp;E345&amp;F345&amp;G345</f>
+        <v>NtrDontSt344.PQTC.27.03.26</v>
+      </c>
+      <c r="L345" s="19" t="str">
+        <f>A345&amp;" "&amp;C345&amp;D345&amp;E345&amp;F345&amp;G345&amp;" "&amp;H345</f>
+        <v>344 NtrDontSt344.PQTC.27.03.26 Dont_Starve_Циклоп-олень</v>
       </c>
     </row>
   </sheetData>
@@ -12951,127 +13572,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -13079,23 +13700,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -13103,23 +13724,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -13127,39 +13748,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -13167,162 +13788,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Артикулы" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="528">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1306,6 +1306,42 @@
   </si>
   <si>
     <t>Dont_Starve_Циклоп-олень</t>
+  </si>
+  <si>
+    <t>ICARUS</t>
+  </si>
+  <si>
+    <t>28.03.26</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_1</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_2</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_3</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_4</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_5</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_6</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_7</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_8</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_9</t>
+  </si>
+  <si>
+    <t>ICARUS_Обложка_10</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2593,23 +2629,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q345"/>
+  <dimension ref="A1:Q355"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
     <col min="2" max="2" width="3.66666666666667" style="6" customWidth="1"/>
     <col min="3" max="3" width="15.3333333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.4351851851852" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.5555555555556" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.4385964912281" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.5526315789474" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.3333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="9.88888888888889" style="8" customWidth="1"/>
-    <col min="8" max="8" width="28.1018518518519" style="6" customWidth="1"/>
-    <col min="9" max="9" width="7.55555555555556" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.8859649122807" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.1052631578947" style="6" customWidth="1"/>
+    <col min="9" max="9" width="7.55263157894737" style="6" customWidth="1"/>
     <col min="10" max="10" width="29.6666666666667" style="6" customWidth="1"/>
     <col min="11" max="11" width="10" style="6"/>
-    <col min="12" max="12" width="66.8888888888889" style="6" customWidth="1"/>
+    <col min="12" max="12" width="66.8859649122807" style="6" customWidth="1"/>
     <col min="13" max="15" width="10" style="6"/>
-    <col min="16" max="16" width="8.88888888888889" style="6" customWidth="1"/>
+    <col min="16" max="16" width="8.8859649122807" style="6" customWidth="1"/>
     <col min="17" max="16384" width="10" style="6"/>
   </cols>
   <sheetData>
@@ -12568,7 +12604,7 @@
         <v>397</v>
       </c>
       <c r="E316" s="6" t="str">
-        <f t="shared" ref="E316:E335" si="12">A316&amp;"."</f>
+        <f t="shared" ref="E316:E345" si="12">A316&amp;"."</f>
         <v>315.</v>
       </c>
       <c r="F316" s="19" t="s">
@@ -12773,11 +12809,11 @@
         <v>407</v>
       </c>
       <c r="J322" s="21" t="str">
-        <f t="shared" ref="J322:J335" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <f t="shared" ref="J322:J345" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
         <v>CupDontSt321.PQTC.26.03.26</v>
       </c>
       <c r="L322" s="19" t="str">
-        <f t="shared" ref="L322:L335" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <f t="shared" ref="L322:L345" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
         <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
       </c>
     </row>
@@ -13208,7 +13244,7 @@
         <v>397</v>
       </c>
       <c r="E336" s="6" t="str">
-        <f>A336&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>335.</v>
       </c>
       <c r="F336" s="19" t="s">
@@ -13221,11 +13257,11 @@
         <v>416</v>
       </c>
       <c r="J336" s="21" t="str">
-        <f>C336&amp;D336&amp;E336&amp;F336&amp;G336</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt335.PQTC.27.03.26</v>
       </c>
       <c r="L336" s="19" t="str">
-        <f>A336&amp;" "&amp;C336&amp;D336&amp;E336&amp;F336&amp;G336&amp;" "&amp;H336</f>
+        <f t="shared" si="14"/>
         <v>335 NtrDontSt335.PQTC.27.03.26 Dont_Starve_Уилсон</v>
       </c>
     </row>
@@ -13240,7 +13276,7 @@
         <v>397</v>
       </c>
       <c r="E337" s="6" t="str">
-        <f>A337&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>336.</v>
       </c>
       <c r="F337" s="19" t="s">
@@ -13253,11 +13289,11 @@
         <v>417</v>
       </c>
       <c r="J337" s="21" t="str">
-        <f>C337&amp;D337&amp;E337&amp;F337&amp;G337</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt336.PQTC.27.03.26</v>
       </c>
       <c r="L337" s="19" t="str">
-        <f>A337&amp;" "&amp;C337&amp;D337&amp;E337&amp;F337&amp;G337&amp;" "&amp;H337</f>
+        <f t="shared" si="14"/>
         <v>336 NtrDontSt336.PQTC.27.03.26 Dont_Starve_Венди</v>
       </c>
     </row>
@@ -13272,7 +13308,7 @@
         <v>397</v>
       </c>
       <c r="E338" s="6" t="str">
-        <f>A338&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>337.</v>
       </c>
       <c r="F338" s="19" t="s">
@@ -13285,11 +13321,11 @@
         <v>418</v>
       </c>
       <c r="J338" s="21" t="str">
-        <f>C338&amp;D338&amp;E338&amp;F338&amp;G338</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt337.PQTC.27.03.26</v>
       </c>
       <c r="L338" s="19" t="str">
-        <f>A338&amp;" "&amp;C338&amp;D338&amp;E338&amp;F338&amp;G338&amp;" "&amp;H338</f>
+        <f t="shared" si="14"/>
         <v>337 NtrDontSt337.PQTC.27.03.26 Dont_Starve_Венди_2</v>
       </c>
     </row>
@@ -13304,7 +13340,7 @@
         <v>397</v>
       </c>
       <c r="E339" s="6" t="str">
-        <f>A339&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>338.</v>
       </c>
       <c r="F339" s="19" t="s">
@@ -13317,11 +13353,11 @@
         <v>419</v>
       </c>
       <c r="J339" s="21" t="str">
-        <f>C339&amp;D339&amp;E339&amp;F339&amp;G339</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt338.PQTC.27.03.26</v>
       </c>
       <c r="L339" s="19" t="str">
-        <f>A339&amp;" "&amp;C339&amp;D339&amp;E339&amp;F339&amp;G339&amp;" "&amp;H339</f>
+        <f t="shared" si="14"/>
         <v>338 NtrDontSt338.PQTC.27.03.26 Dont_Starve_ Уиллоу</v>
       </c>
     </row>
@@ -13336,7 +13372,7 @@
         <v>397</v>
       </c>
       <c r="E340" s="6" t="str">
-        <f>A340&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>339.</v>
       </c>
       <c r="F340" s="19" t="s">
@@ -13349,11 +13385,11 @@
         <v>420</v>
       </c>
       <c r="J340" s="21" t="str">
-        <f>C340&amp;D340&amp;E340&amp;F340&amp;G340</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt339.PQTC.27.03.26</v>
       </c>
       <c r="L340" s="19" t="str">
-        <f>A340&amp;" "&amp;C340&amp;D340&amp;E340&amp;F340&amp;G340&amp;" "&amp;H340</f>
+        <f t="shared" si="14"/>
         <v>339 NtrDontSt339.PQTC.27.03.26 Dont_Starve_ Уиллоу_2</v>
       </c>
     </row>
@@ -13368,7 +13404,7 @@
         <v>397</v>
       </c>
       <c r="E341" s="6" t="str">
-        <f>A341&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>340.</v>
       </c>
       <c r="F341" s="19" t="s">
@@ -13381,11 +13417,11 @@
         <v>421</v>
       </c>
       <c r="J341" s="21" t="str">
-        <f>C341&amp;D341&amp;E341&amp;F341&amp;G341</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt340.PQTC.27.03.26</v>
       </c>
       <c r="L341" s="19" t="str">
-        <f>A341&amp;" "&amp;C341&amp;D341&amp;E341&amp;F341&amp;G341&amp;" "&amp;H341</f>
+        <f t="shared" si="14"/>
         <v>340 NtrDontSt340.PQTC.27.03.26 Dont_Starve_ Уиллоу_3</v>
       </c>
     </row>
@@ -13400,7 +13436,7 @@
         <v>397</v>
       </c>
       <c r="E342" s="6" t="str">
-        <f>A342&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>341.</v>
       </c>
       <c r="F342" s="19" t="s">
@@ -13413,11 +13449,11 @@
         <v>422</v>
       </c>
       <c r="J342" s="21" t="str">
-        <f>C342&amp;D342&amp;E342&amp;F342&amp;G342</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt341.PQTC.27.03.26</v>
       </c>
       <c r="L342" s="19" t="str">
-        <f>A342&amp;" "&amp;C342&amp;D342&amp;E342&amp;F342&amp;G342&amp;" "&amp;H342</f>
+        <f t="shared" si="14"/>
         <v>341 NtrDontSt341.PQTC.27.03.26 Dont_Starve_Вуди</v>
       </c>
     </row>
@@ -13432,7 +13468,7 @@
         <v>397</v>
       </c>
       <c r="E343" s="6" t="str">
-        <f>A343&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>342.</v>
       </c>
       <c r="F343" s="19" t="s">
@@ -13445,11 +13481,11 @@
         <v>423</v>
       </c>
       <c r="J343" s="21" t="str">
-        <f>C343&amp;D343&amp;E343&amp;F343&amp;G343</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt342.PQTC.27.03.26</v>
       </c>
       <c r="L343" s="19" t="str">
-        <f>A343&amp;" "&amp;C343&amp;D343&amp;E343&amp;F343&amp;G343&amp;" "&amp;H343</f>
+        <f t="shared" si="14"/>
         <v>342 NtrDontSt342.PQTC.27.03.26 Dont_Starve_Персонажи</v>
       </c>
     </row>
@@ -13464,7 +13500,7 @@
         <v>397</v>
       </c>
       <c r="E344" s="6" t="str">
-        <f>A344&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>343.</v>
       </c>
       <c r="F344" s="19" t="s">
@@ -13477,11 +13513,11 @@
         <v>424</v>
       </c>
       <c r="J344" s="21" t="str">
-        <f>C344&amp;D344&amp;E344&amp;F344&amp;G344</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt343.PQTC.27.03.26</v>
       </c>
       <c r="L344" s="19" t="str">
-        <f>A344&amp;" "&amp;C344&amp;D344&amp;E344&amp;F344&amp;G344&amp;" "&amp;H344</f>
+        <f t="shared" si="14"/>
         <v>343 NtrDontSt343.PQTC.27.03.26 Dont_Starve_Персонажи_2</v>
       </c>
     </row>
@@ -13496,7 +13532,7 @@
         <v>397</v>
       </c>
       <c r="E345" s="6" t="str">
-        <f>A345&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>344.</v>
       </c>
       <c r="F345" s="19" t="s">
@@ -13509,12 +13545,332 @@
         <v>425</v>
       </c>
       <c r="J345" s="21" t="str">
-        <f>C345&amp;D345&amp;E345&amp;F345&amp;G345</f>
+        <f t="shared" si="13"/>
         <v>NtrDontSt344.PQTC.27.03.26</v>
       </c>
       <c r="L345" s="19" t="str">
-        <f>A345&amp;" "&amp;C345&amp;D345&amp;E345&amp;F345&amp;G345&amp;" "&amp;H345</f>
+        <f t="shared" si="14"/>
         <v>344 NtrDontSt344.PQTC.27.03.26 Dont_Starve_Циклоп-олень</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12">
+      <c r="A346" s="5">
+        <v>345</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D346" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E346" s="6" t="str">
+        <f>A346&amp;"."</f>
+        <v>345.</v>
+      </c>
+      <c r="F346" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G346" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H346" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="J346" s="21" t="str">
+        <f>C346&amp;D346&amp;E346&amp;F346&amp;G346</f>
+        <v>CupICARUS345.PQTC.28.03.26</v>
+      </c>
+      <c r="L346" s="19" t="str">
+        <f>A346&amp;" "&amp;C346&amp;D346&amp;E346&amp;F346&amp;G346&amp;" "&amp;H346</f>
+        <v>345 CupICARUS345.PQTC.28.03.26 ICARUS_Обложка_1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12">
+      <c r="A347" s="5">
+        <v>346</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D347" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E347" s="6" t="str">
+        <f>A347&amp;"."</f>
+        <v>346.</v>
+      </c>
+      <c r="F347" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G347" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H347" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="J347" s="21" t="str">
+        <f>C347&amp;D347&amp;E347&amp;F347&amp;G347</f>
+        <v>CupICARUS346.PQTC.28.03.26</v>
+      </c>
+      <c r="L347" s="19" t="str">
+        <f>A347&amp;" "&amp;C347&amp;D347&amp;E347&amp;F347&amp;G347&amp;" "&amp;H347</f>
+        <v>346 CupICARUS346.PQTC.28.03.26 ICARUS_Обложка_2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12">
+      <c r="A348" s="5">
+        <v>347</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D348" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E348" s="6" t="str">
+        <f>A348&amp;"."</f>
+        <v>347.</v>
+      </c>
+      <c r="F348" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G348" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H348" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="J348" s="21" t="str">
+        <f>C348&amp;D348&amp;E348&amp;F348&amp;G348</f>
+        <v>CupICARUS347.PQTC.28.03.26</v>
+      </c>
+      <c r="L348" s="19" t="str">
+        <f>A348&amp;" "&amp;C348&amp;D348&amp;E348&amp;F348&amp;G348&amp;" "&amp;H348</f>
+        <v>347 CupICARUS347.PQTC.28.03.26 ICARUS_Обложка_3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12">
+      <c r="A349" s="5">
+        <v>348</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D349" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E349" s="6" t="str">
+        <f>A349&amp;"."</f>
+        <v>348.</v>
+      </c>
+      <c r="F349" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G349" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H349" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J349" s="21" t="str">
+        <f>C349&amp;D349&amp;E349&amp;F349&amp;G349</f>
+        <v>CupICARUS348.PQTC.28.03.26</v>
+      </c>
+      <c r="L349" s="19" t="str">
+        <f>A349&amp;" "&amp;C349&amp;D349&amp;E349&amp;F349&amp;G349&amp;" "&amp;H349</f>
+        <v>348 CupICARUS348.PQTC.28.03.26 ICARUS_Обложка_4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12">
+      <c r="A350" s="5">
+        <v>349</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D350" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E350" s="6" t="str">
+        <f>A350&amp;"."</f>
+        <v>349.</v>
+      </c>
+      <c r="F350" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G350" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H350" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J350" s="21" t="str">
+        <f>C350&amp;D350&amp;E350&amp;F350&amp;G350</f>
+        <v>CupICARUS349.PQTC.28.03.26</v>
+      </c>
+      <c r="L350" s="19" t="str">
+        <f>A350&amp;" "&amp;C350&amp;D350&amp;E350&amp;F350&amp;G350&amp;" "&amp;H350</f>
+        <v>349 CupICARUS349.PQTC.28.03.26 ICARUS_Обложка_5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12">
+      <c r="A351" s="5">
+        <v>350</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D351" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E351" s="6" t="str">
+        <f>A351&amp;"."</f>
+        <v>350.</v>
+      </c>
+      <c r="F351" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G351" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H351" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="J351" s="21" t="str">
+        <f>C351&amp;D351&amp;E351&amp;F351&amp;G351</f>
+        <v>CupICARUS350.PQTC.28.03.26</v>
+      </c>
+      <c r="L351" s="19" t="str">
+        <f>A351&amp;" "&amp;C351&amp;D351&amp;E351&amp;F351&amp;G351&amp;" "&amp;H351</f>
+        <v>350 CupICARUS350.PQTC.28.03.26 ICARUS_Обложка_6</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12">
+      <c r="A352" s="5">
+        <v>351</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D352" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E352" s="6" t="str">
+        <f>A352&amp;"."</f>
+        <v>351.</v>
+      </c>
+      <c r="F352" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G352" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H352" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="J352" s="21" t="str">
+        <f>C352&amp;D352&amp;E352&amp;F352&amp;G352</f>
+        <v>CupICARUS351.PQTC.28.03.26</v>
+      </c>
+      <c r="L352" s="19" t="str">
+        <f>A352&amp;" "&amp;C352&amp;D352&amp;E352&amp;F352&amp;G352&amp;" "&amp;H352</f>
+        <v>351 CupICARUS351.PQTC.28.03.26 ICARUS_Обложка_7</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12">
+      <c r="A353" s="5">
+        <v>352</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D353" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E353" s="6" t="str">
+        <f>A353&amp;"."</f>
+        <v>352.</v>
+      </c>
+      <c r="F353" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G353" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H353" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="J353" s="21" t="str">
+        <f>C353&amp;D353&amp;E353&amp;F353&amp;G353</f>
+        <v>CupICARUS352.PQTC.28.03.26</v>
+      </c>
+      <c r="L353" s="19" t="str">
+        <f>A353&amp;" "&amp;C353&amp;D353&amp;E353&amp;F353&amp;G353&amp;" "&amp;H353</f>
+        <v>352 CupICARUS352.PQTC.28.03.26 ICARUS_Обложка_8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12">
+      <c r="A354" s="5">
+        <v>353</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D354" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E354" s="6" t="str">
+        <f>A354&amp;"."</f>
+        <v>353.</v>
+      </c>
+      <c r="F354" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G354" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H354" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="J354" s="21" t="str">
+        <f>C354&amp;D354&amp;E354&amp;F354&amp;G354</f>
+        <v>CupICARUS353.PQTC.28.03.26</v>
+      </c>
+      <c r="L354" s="19" t="str">
+        <f>A354&amp;" "&amp;C354&amp;D354&amp;E354&amp;F354&amp;G354&amp;" "&amp;H354</f>
+        <v>353 CupICARUS353.PQTC.28.03.26 ICARUS_Обложка_9</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12">
+      <c r="A355" s="5">
+        <v>354</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E355" s="6" t="str">
+        <f>A355&amp;"."</f>
+        <v>354.</v>
+      </c>
+      <c r="F355" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G355" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H355" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="J355" s="21" t="str">
+        <f>C355&amp;D355&amp;E355&amp;F355&amp;G355</f>
+        <v>CupICARUS354.PQTC.28.03.26</v>
+      </c>
+      <c r="L355" s="19" t="str">
+        <f>A355&amp;" "&amp;C355&amp;D355&amp;E355&amp;F355&amp;G355&amp;" "&amp;H355</f>
+        <v>354 CupICARUS354.PQTC.28.03.26 ICARUS_Обложка_10</v>
       </c>
     </row>
   </sheetData>
@@ -13563,136 +13919,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9.10185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9.10526315789474" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="45.1018518518519" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.10185185185185" style="1"/>
+    <col min="1" max="1" width="45.1052631578947" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.8859649122807" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.10526315789474" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" ht="31.95" spans="1:2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -13700,23 +14056,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -13724,23 +14080,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -13748,39 +14104,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -13788,162 +14144,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="541">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1342,6 +1342,45 @@
   </si>
   <si>
     <t>ICARUS_Обложка_10</t>
+  </si>
+  <si>
+    <t>29.03.26</t>
+  </si>
+  <si>
+    <t>ICARUS_Сердце</t>
+  </si>
+  <si>
+    <t>ICARUS_Медведь</t>
+  </si>
+  <si>
+    <t>ICARUS_Астронавты</t>
+  </si>
+  <si>
+    <t>ICARUS_Оазис</t>
+  </si>
+  <si>
+    <t>ICARUS_Пикник</t>
+  </si>
+  <si>
+    <t>ICARUS_Верстак</t>
+  </si>
+  <si>
+    <t>ICARUS_Грибы</t>
+  </si>
+  <si>
+    <t>ICARUS_Равнины</t>
+  </si>
+  <si>
+    <t>ICARUS_Лава</t>
+  </si>
+  <si>
+    <t>ICARUS_Лес</t>
+  </si>
+  <si>
+    <t>ICARUS_Фауна</t>
+  </si>
+  <si>
+    <t>ICARUS_Горы</t>
   </si>
   <si>
     <t>Товар</t>
@@ -2629,7 +2668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q355"/>
+  <dimension ref="A1:Q367"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
@@ -12604,7 +12643,7 @@
         <v>397</v>
       </c>
       <c r="E316" s="6" t="str">
-        <f t="shared" ref="E316:E345" si="12">A316&amp;"."</f>
+        <f t="shared" ref="E316:E358" si="12">A316&amp;"."</f>
         <v>315.</v>
       </c>
       <c r="F316" s="19" t="s">
@@ -12809,11 +12848,11 @@
         <v>407</v>
       </c>
       <c r="J322" s="21" t="str">
-        <f t="shared" ref="J322:J345" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <f t="shared" ref="J322:J358" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
         <v>CupDontSt321.PQTC.26.03.26</v>
       </c>
       <c r="L322" s="19" t="str">
-        <f t="shared" ref="L322:L345" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <f t="shared" ref="L322:L358" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
         <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
       </c>
     </row>
@@ -13564,7 +13603,7 @@
         <v>426</v>
       </c>
       <c r="E346" s="6" t="str">
-        <f>A346&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>345.</v>
       </c>
       <c r="F346" s="19" t="s">
@@ -13577,11 +13616,11 @@
         <v>428</v>
       </c>
       <c r="J346" s="21" t="str">
-        <f>C346&amp;D346&amp;E346&amp;F346&amp;G346</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS345.PQTC.28.03.26</v>
       </c>
       <c r="L346" s="19" t="str">
-        <f>A346&amp;" "&amp;C346&amp;D346&amp;E346&amp;F346&amp;G346&amp;" "&amp;H346</f>
+        <f t="shared" si="14"/>
         <v>345 CupICARUS345.PQTC.28.03.26 ICARUS_Обложка_1</v>
       </c>
     </row>
@@ -13596,7 +13635,7 @@
         <v>426</v>
       </c>
       <c r="E347" s="6" t="str">
-        <f>A347&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>346.</v>
       </c>
       <c r="F347" s="19" t="s">
@@ -13609,11 +13648,11 @@
         <v>429</v>
       </c>
       <c r="J347" s="21" t="str">
-        <f>C347&amp;D347&amp;E347&amp;F347&amp;G347</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS346.PQTC.28.03.26</v>
       </c>
       <c r="L347" s="19" t="str">
-        <f>A347&amp;" "&amp;C347&amp;D347&amp;E347&amp;F347&amp;G347&amp;" "&amp;H347</f>
+        <f t="shared" si="14"/>
         <v>346 CupICARUS346.PQTC.28.03.26 ICARUS_Обложка_2</v>
       </c>
     </row>
@@ -13628,7 +13667,7 @@
         <v>426</v>
       </c>
       <c r="E348" s="6" t="str">
-        <f>A348&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>347.</v>
       </c>
       <c r="F348" s="19" t="s">
@@ -13641,11 +13680,11 @@
         <v>430</v>
       </c>
       <c r="J348" s="21" t="str">
-        <f>C348&amp;D348&amp;E348&amp;F348&amp;G348</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS347.PQTC.28.03.26</v>
       </c>
       <c r="L348" s="19" t="str">
-        <f>A348&amp;" "&amp;C348&amp;D348&amp;E348&amp;F348&amp;G348&amp;" "&amp;H348</f>
+        <f t="shared" si="14"/>
         <v>347 CupICARUS347.PQTC.28.03.26 ICARUS_Обложка_3</v>
       </c>
     </row>
@@ -13660,7 +13699,7 @@
         <v>426</v>
       </c>
       <c r="E349" s="6" t="str">
-        <f>A349&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>348.</v>
       </c>
       <c r="F349" s="19" t="s">
@@ -13673,11 +13712,11 @@
         <v>431</v>
       </c>
       <c r="J349" s="21" t="str">
-        <f>C349&amp;D349&amp;E349&amp;F349&amp;G349</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS348.PQTC.28.03.26</v>
       </c>
       <c r="L349" s="19" t="str">
-        <f>A349&amp;" "&amp;C349&amp;D349&amp;E349&amp;F349&amp;G349&amp;" "&amp;H349</f>
+        <f t="shared" si="14"/>
         <v>348 CupICARUS348.PQTC.28.03.26 ICARUS_Обложка_4</v>
       </c>
     </row>
@@ -13692,7 +13731,7 @@
         <v>426</v>
       </c>
       <c r="E350" s="6" t="str">
-        <f>A350&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>349.</v>
       </c>
       <c r="F350" s="19" t="s">
@@ -13705,11 +13744,11 @@
         <v>432</v>
       </c>
       <c r="J350" s="21" t="str">
-        <f>C350&amp;D350&amp;E350&amp;F350&amp;G350</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS349.PQTC.28.03.26</v>
       </c>
       <c r="L350" s="19" t="str">
-        <f>A350&amp;" "&amp;C350&amp;D350&amp;E350&amp;F350&amp;G350&amp;" "&amp;H350</f>
+        <f t="shared" si="14"/>
         <v>349 CupICARUS349.PQTC.28.03.26 ICARUS_Обложка_5</v>
       </c>
     </row>
@@ -13724,7 +13763,7 @@
         <v>426</v>
       </c>
       <c r="E351" s="6" t="str">
-        <f>A351&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>350.</v>
       </c>
       <c r="F351" s="19" t="s">
@@ -13737,11 +13776,11 @@
         <v>433</v>
       </c>
       <c r="J351" s="21" t="str">
-        <f>C351&amp;D351&amp;E351&amp;F351&amp;G351</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS350.PQTC.28.03.26</v>
       </c>
       <c r="L351" s="19" t="str">
-        <f>A351&amp;" "&amp;C351&amp;D351&amp;E351&amp;F351&amp;G351&amp;" "&amp;H351</f>
+        <f t="shared" si="14"/>
         <v>350 CupICARUS350.PQTC.28.03.26 ICARUS_Обложка_6</v>
       </c>
     </row>
@@ -13756,7 +13795,7 @@
         <v>426</v>
       </c>
       <c r="E352" s="6" t="str">
-        <f>A352&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>351.</v>
       </c>
       <c r="F352" s="19" t="s">
@@ -13769,11 +13808,11 @@
         <v>434</v>
       </c>
       <c r="J352" s="21" t="str">
-        <f>C352&amp;D352&amp;E352&amp;F352&amp;G352</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS351.PQTC.28.03.26</v>
       </c>
       <c r="L352" s="19" t="str">
-        <f>A352&amp;" "&amp;C352&amp;D352&amp;E352&amp;F352&amp;G352&amp;" "&amp;H352</f>
+        <f t="shared" si="14"/>
         <v>351 CupICARUS351.PQTC.28.03.26 ICARUS_Обложка_7</v>
       </c>
     </row>
@@ -13788,7 +13827,7 @@
         <v>426</v>
       </c>
       <c r="E353" s="6" t="str">
-        <f>A353&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>352.</v>
       </c>
       <c r="F353" s="19" t="s">
@@ -13801,11 +13840,11 @@
         <v>435</v>
       </c>
       <c r="J353" s="21" t="str">
-        <f>C353&amp;D353&amp;E353&amp;F353&amp;G353</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS352.PQTC.28.03.26</v>
       </c>
       <c r="L353" s="19" t="str">
-        <f>A353&amp;" "&amp;C353&amp;D353&amp;E353&amp;F353&amp;G353&amp;" "&amp;H353</f>
+        <f t="shared" si="14"/>
         <v>352 CupICARUS352.PQTC.28.03.26 ICARUS_Обложка_8</v>
       </c>
     </row>
@@ -13820,7 +13859,7 @@
         <v>426</v>
       </c>
       <c r="E354" s="6" t="str">
-        <f>A354&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>353.</v>
       </c>
       <c r="F354" s="19" t="s">
@@ -13833,11 +13872,11 @@
         <v>436</v>
       </c>
       <c r="J354" s="21" t="str">
-        <f>C354&amp;D354&amp;E354&amp;F354&amp;G354</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS353.PQTC.28.03.26</v>
       </c>
       <c r="L354" s="19" t="str">
-        <f>A354&amp;" "&amp;C354&amp;D354&amp;E354&amp;F354&amp;G354&amp;" "&amp;H354</f>
+        <f t="shared" si="14"/>
         <v>353 CupICARUS353.PQTC.28.03.26 ICARUS_Обложка_9</v>
       </c>
     </row>
@@ -13852,7 +13891,7 @@
         <v>426</v>
       </c>
       <c r="E355" s="6" t="str">
-        <f>A355&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>354.</v>
       </c>
       <c r="F355" s="19" t="s">
@@ -13865,12 +13904,396 @@
         <v>437</v>
       </c>
       <c r="J355" s="21" t="str">
-        <f>C355&amp;D355&amp;E355&amp;F355&amp;G355</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS354.PQTC.28.03.26</v>
       </c>
       <c r="L355" s="19" t="str">
-        <f>A355&amp;" "&amp;C355&amp;D355&amp;E355&amp;F355&amp;G355&amp;" "&amp;H355</f>
+        <f t="shared" si="14"/>
         <v>354 CupICARUS354.PQTC.28.03.26 ICARUS_Обложка_10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12">
+      <c r="A356" s="5">
+        <v>355</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D356" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E356" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>355.</v>
+      </c>
+      <c r="F356" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G356" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H356" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="J356" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>CupICARUS355.PQTC.29.03.26</v>
+      </c>
+      <c r="L356" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>355 CupICARUS355.PQTC.29.03.26 ICARUS_Сердце</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12">
+      <c r="A357" s="5">
+        <v>356</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D357" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E357" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>356.</v>
+      </c>
+      <c r="F357" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G357" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H357" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="J357" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>CupICARUS356.PQTC.29.03.26</v>
+      </c>
+      <c r="L357" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>356 CupICARUS356.PQTC.29.03.26 ICARUS_Медведь</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12">
+      <c r="A358" s="5">
+        <v>357</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D358" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E358" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>357.</v>
+      </c>
+      <c r="F358" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G358" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H358" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="J358" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v>CupICARUS357.PQTC.29.03.26</v>
+      </c>
+      <c r="L358" s="19" t="str">
+        <f t="shared" si="14"/>
+        <v>357 CupICARUS357.PQTC.29.03.26 ICARUS_Астронавты</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12">
+      <c r="A359" s="5">
+        <v>358</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D359" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E359" s="6" t="str">
+        <f>A359&amp;"."</f>
+        <v>358.</v>
+      </c>
+      <c r="F359" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G359" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H359" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="J359" s="21" t="str">
+        <f>C359&amp;D359&amp;E359&amp;F359&amp;G359</f>
+        <v>CupICARUS358.PQTC.29.03.26</v>
+      </c>
+      <c r="L359" s="19" t="str">
+        <f>A359&amp;" "&amp;C359&amp;D359&amp;E359&amp;F359&amp;G359&amp;" "&amp;H359</f>
+        <v>358 CupICARUS358.PQTC.29.03.26 ICARUS_Оазис</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12">
+      <c r="A360" s="5">
+        <v>359</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D360" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E360" s="6" t="str">
+        <f>A360&amp;"."</f>
+        <v>359.</v>
+      </c>
+      <c r="F360" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G360" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H360" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J360" s="21" t="str">
+        <f>C360&amp;D360&amp;E360&amp;F360&amp;G360</f>
+        <v>CupICARUS359.PQTC.29.03.26</v>
+      </c>
+      <c r="L360" s="19" t="str">
+        <f>A360&amp;" "&amp;C360&amp;D360&amp;E360&amp;F360&amp;G360&amp;" "&amp;H360</f>
+        <v>359 CupICARUS359.PQTC.29.03.26 ICARUS_Пикник</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12">
+      <c r="A361" s="5">
+        <v>360</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D361" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E361" s="6" t="str">
+        <f>A361&amp;"."</f>
+        <v>360.</v>
+      </c>
+      <c r="F361" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G361" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H361" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="J361" s="21" t="str">
+        <f>C361&amp;D361&amp;E361&amp;F361&amp;G361</f>
+        <v>CupICARUS360.PQTC.29.03.26</v>
+      </c>
+      <c r="L361" s="19" t="str">
+        <f>A361&amp;" "&amp;C361&amp;D361&amp;E361&amp;F361&amp;G361&amp;" "&amp;H361</f>
+        <v>360 CupICARUS360.PQTC.29.03.26 ICARUS_Верстак</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12">
+      <c r="A362" s="5">
+        <v>361</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D362" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E362" s="6" t="str">
+        <f>A362&amp;"."</f>
+        <v>361.</v>
+      </c>
+      <c r="F362" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G362" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H362" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="J362" s="21" t="str">
+        <f>C362&amp;D362&amp;E362&amp;F362&amp;G362</f>
+        <v>CupICARUS361.PQTC.29.03.26</v>
+      </c>
+      <c r="L362" s="19" t="str">
+        <f>A362&amp;" "&amp;C362&amp;D362&amp;E362&amp;F362&amp;G362&amp;" "&amp;H362</f>
+        <v>361 CupICARUS361.PQTC.29.03.26 ICARUS_Грибы</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12">
+      <c r="A363" s="5">
+        <v>362</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D363" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E363" s="6" t="str">
+        <f>A363&amp;"."</f>
+        <v>362.</v>
+      </c>
+      <c r="F363" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G363" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H363" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="J363" s="21" t="str">
+        <f>C363&amp;D363&amp;E363&amp;F363&amp;G363</f>
+        <v>CupICARUS362.PQTC.29.03.26</v>
+      </c>
+      <c r="L363" s="19" t="str">
+        <f>A363&amp;" "&amp;C363&amp;D363&amp;E363&amp;F363&amp;G363&amp;" "&amp;H363</f>
+        <v>362 CupICARUS362.PQTC.29.03.26 ICARUS_Равнины</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12">
+      <c r="A364" s="5">
+        <v>363</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D364" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E364" s="6" t="str">
+        <f>A364&amp;"."</f>
+        <v>363.</v>
+      </c>
+      <c r="F364" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G364" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H364" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="J364" s="21" t="str">
+        <f>C364&amp;D364&amp;E364&amp;F364&amp;G364</f>
+        <v>CupICARUS363.PQTC.29.03.26</v>
+      </c>
+      <c r="L364" s="19" t="str">
+        <f>A364&amp;" "&amp;C364&amp;D364&amp;E364&amp;F364&amp;G364&amp;" "&amp;H364</f>
+        <v>363 CupICARUS363.PQTC.29.03.26 ICARUS_Лава</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12">
+      <c r="A365" s="5">
+        <v>364</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E365" s="6" t="str">
+        <f>A365&amp;"."</f>
+        <v>364.</v>
+      </c>
+      <c r="F365" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G365" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H365" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="J365" s="21" t="str">
+        <f>C365&amp;D365&amp;E365&amp;F365&amp;G365</f>
+        <v>CupICARUS364.PQTC.29.03.26</v>
+      </c>
+      <c r="L365" s="19" t="str">
+        <f>A365&amp;" "&amp;C365&amp;D365&amp;E365&amp;F365&amp;G365&amp;" "&amp;H365</f>
+        <v>364 CupICARUS364.PQTC.29.03.26 ICARUS_Лес</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12">
+      <c r="A366" s="5">
+        <v>365</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D366" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E366" s="6" t="str">
+        <f>A366&amp;"."</f>
+        <v>365.</v>
+      </c>
+      <c r="F366" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G366" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H366" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J366" s="21" t="str">
+        <f>C366&amp;D366&amp;E366&amp;F366&amp;G366</f>
+        <v>CupICARUS365.PQTC.29.03.26</v>
+      </c>
+      <c r="L366" s="19" t="str">
+        <f>A366&amp;" "&amp;C366&amp;D366&amp;E366&amp;F366&amp;G366&amp;" "&amp;H366</f>
+        <v>365 CupICARUS365.PQTC.29.03.26 ICARUS_Фауна</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12">
+      <c r="A367" s="5">
+        <v>366</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D367" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E367" s="6" t="str">
+        <f>A367&amp;"."</f>
+        <v>366.</v>
+      </c>
+      <c r="F367" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G367" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="H367" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="J367" s="21" t="str">
+        <f>C367&amp;D367&amp;E367&amp;F367&amp;G367</f>
+        <v>CupICARUS366.PQTC.29.03.26</v>
+      </c>
+      <c r="L367" s="19" t="str">
+        <f>A367&amp;" "&amp;C367&amp;D367&amp;E367&amp;F367&amp;G367&amp;" "&amp;H367</f>
+        <v>366 CupICARUS366.PQTC.29.03.26 ICARUS_Горы</v>
       </c>
     </row>
   </sheetData>
@@ -13928,127 +14351,127 @@
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -14056,23 +14479,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -14080,23 +14503,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -14104,39 +14527,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -14144,162 +14567,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9150"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Артикулы" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="546">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1381,6 +1381,21 @@
   </si>
   <si>
     <t>ICARUS_Горы</t>
+  </si>
+  <si>
+    <t>30.03.26</t>
+  </si>
+  <si>
+    <t>ICARUS_Лагерь</t>
+  </si>
+  <si>
+    <t>ICARUS_Космос</t>
+  </si>
+  <si>
+    <t>ICARUS_Олень</t>
+  </si>
+  <si>
+    <t>ICARUS_Луга</t>
   </si>
   <si>
     <t>Товар</t>
@@ -1663,7 +1678,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1709,6 +1724,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -2202,16 +2223,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2220,119 +2238,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2344,59 +2365,65 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2668,23 +2695,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q367"/>
+  <dimension ref="A1:Q377"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
     <col min="2" max="2" width="3.66666666666667" style="6" customWidth="1"/>
     <col min="3" max="3" width="15.3333333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.4385964912281" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.5526315789474" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.4351851851852" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.5555555555556" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.3333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="9.8859649122807" style="8" customWidth="1"/>
-    <col min="8" max="8" width="28.1052631578947" style="6" customWidth="1"/>
-    <col min="9" max="9" width="7.55263157894737" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.88888888888889" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.1018518518519" style="6" customWidth="1"/>
+    <col min="9" max="9" width="7.55555555555556" style="6" customWidth="1"/>
     <col min="10" max="10" width="29.6666666666667" style="6" customWidth="1"/>
     <col min="11" max="11" width="10" style="6"/>
-    <col min="12" max="12" width="66.8859649122807" style="6" customWidth="1"/>
+    <col min="12" max="12" width="66.8888888888889" style="6" customWidth="1"/>
     <col min="13" max="15" width="10" style="6"/>
-    <col min="16" max="16" width="8.8859649122807" style="6" customWidth="1"/>
+    <col min="16" max="16" width="8.88888888888889" style="6" customWidth="1"/>
     <col min="17" max="16384" width="10" style="6"/>
   </cols>
   <sheetData>
@@ -2720,7 +2747,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="16.35" spans="1:12">
+    <row r="2" ht="15.6" spans="1:12">
       <c r="A2" s="12" t="s">
         <v>9</v>
       </c>
@@ -2752,7 +2779,7 @@
         <v>01 NtrDeathG01.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
-    <row r="3" ht="16.35" spans="1:12">
+    <row r="3" ht="15.6" spans="1:12">
       <c r="A3" s="12" t="s">
         <v>16</v>
       </c>
@@ -2784,7 +2811,7 @@
         <v>02 NtrDeathG02.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
-    <row r="4" ht="16.35" spans="1:12">
+    <row r="4" ht="15.6" spans="1:12">
       <c r="A4" s="12" t="s">
         <v>18</v>
       </c>
@@ -2816,7 +2843,7 @@
         <v>03 KgrMadona03.PQTC.26.02.26 Мадонна</v>
       </c>
     </row>
-    <row r="5" ht="16.35" spans="1:12">
+    <row r="5" ht="15.6" spans="1:12">
       <c r="A5" s="12" t="s">
         <v>23</v>
       </c>
@@ -2848,7 +2875,7 @@
         <v>04 KgrMadona04.PQTC.26.02.26 Мадонна</v>
       </c>
     </row>
-    <row r="6" ht="16.35" spans="1:12">
+    <row r="6" ht="15.6" spans="1:12">
       <c r="A6" s="12" t="s">
         <v>25</v>
       </c>
@@ -2880,7 +2907,7 @@
         <v>05 KgrMadona05.PQTC.26.02.26 Мадонна</v>
       </c>
     </row>
-    <row r="7" ht="16.35" spans="1:12">
+    <row r="7" ht="15.6" spans="1:12">
       <c r="A7" s="12" t="s">
         <v>27</v>
       </c>
@@ -2912,7 +2939,7 @@
         <v>06 NtrDeathG06.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
-    <row r="8" ht="16.35" spans="1:12">
+    <row r="8" ht="15.6" spans="1:12">
       <c r="A8" s="12" t="s">
         <v>29</v>
       </c>
@@ -2944,7 +2971,7 @@
         <v>07 NtrDeathG07.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
-    <row r="9" ht="16.35" spans="1:12">
+    <row r="9" ht="15.6" spans="1:12">
       <c r="A9" s="12" t="s">
         <v>31</v>
       </c>
@@ -2976,7 +3003,7 @@
         <v>08 NtrDeathG08.PQTC.26.02.26 сериал Игра Смерти</v>
       </c>
     </row>
-    <row r="10" ht="16.35" spans="1:12">
+    <row r="10" ht="15.6" spans="1:12">
       <c r="A10" s="12" t="s">
         <v>33</v>
       </c>
@@ -3008,7 +3035,7 @@
         <v>09 KgrBMWTou09.PQTC.26.02.26 BMW М5 Touring</v>
       </c>
     </row>
-    <row r="11" ht="16.35" spans="1:12">
+    <row r="11" ht="15.6" spans="1:12">
       <c r="A11" s="12" t="s">
         <v>37</v>
       </c>
@@ -12643,7 +12670,7 @@
         <v>397</v>
       </c>
       <c r="E316" s="6" t="str">
-        <f t="shared" ref="E316:E358" si="12">A316&amp;"."</f>
+        <f t="shared" ref="E316:E367" si="12">A316&amp;"."</f>
         <v>315.</v>
       </c>
       <c r="F316" s="19" t="s">
@@ -12848,11 +12875,11 @@
         <v>407</v>
       </c>
       <c r="J322" s="21" t="str">
-        <f t="shared" ref="J322:J358" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <f t="shared" ref="J322:J367" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
         <v>CupDontSt321.PQTC.26.03.26</v>
       </c>
       <c r="L322" s="19" t="str">
-        <f t="shared" ref="L322:L358" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <f t="shared" ref="L322:L367" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
         <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
       </c>
     </row>
@@ -14019,7 +14046,7 @@
         <v>426</v>
       </c>
       <c r="E359" s="6" t="str">
-        <f>A359&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>358.</v>
       </c>
       <c r="F359" s="19" t="s">
@@ -14032,11 +14059,11 @@
         <v>442</v>
       </c>
       <c r="J359" s="21" t="str">
-        <f>C359&amp;D359&amp;E359&amp;F359&amp;G359</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS358.PQTC.29.03.26</v>
       </c>
       <c r="L359" s="19" t="str">
-        <f>A359&amp;" "&amp;C359&amp;D359&amp;E359&amp;F359&amp;G359&amp;" "&amp;H359</f>
+        <f t="shared" si="14"/>
         <v>358 CupICARUS358.PQTC.29.03.26 ICARUS_Оазис</v>
       </c>
     </row>
@@ -14051,7 +14078,7 @@
         <v>426</v>
       </c>
       <c r="E360" s="6" t="str">
-        <f>A360&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>359.</v>
       </c>
       <c r="F360" s="19" t="s">
@@ -14064,11 +14091,11 @@
         <v>443</v>
       </c>
       <c r="J360" s="21" t="str">
-        <f>C360&amp;D360&amp;E360&amp;F360&amp;G360</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS359.PQTC.29.03.26</v>
       </c>
       <c r="L360" s="19" t="str">
-        <f>A360&amp;" "&amp;C360&amp;D360&amp;E360&amp;F360&amp;G360&amp;" "&amp;H360</f>
+        <f t="shared" si="14"/>
         <v>359 CupICARUS359.PQTC.29.03.26 ICARUS_Пикник</v>
       </c>
     </row>
@@ -14083,7 +14110,7 @@
         <v>426</v>
       </c>
       <c r="E361" s="6" t="str">
-        <f>A361&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>360.</v>
       </c>
       <c r="F361" s="19" t="s">
@@ -14096,11 +14123,11 @@
         <v>444</v>
       </c>
       <c r="J361" s="21" t="str">
-        <f>C361&amp;D361&amp;E361&amp;F361&amp;G361</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS360.PQTC.29.03.26</v>
       </c>
       <c r="L361" s="19" t="str">
-        <f>A361&amp;" "&amp;C361&amp;D361&amp;E361&amp;F361&amp;G361&amp;" "&amp;H361</f>
+        <f t="shared" si="14"/>
         <v>360 CupICARUS360.PQTC.29.03.26 ICARUS_Верстак</v>
       </c>
     </row>
@@ -14115,7 +14142,7 @@
         <v>426</v>
       </c>
       <c r="E362" s="6" t="str">
-        <f>A362&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>361.</v>
       </c>
       <c r="F362" s="19" t="s">
@@ -14128,11 +14155,11 @@
         <v>445</v>
       </c>
       <c r="J362" s="21" t="str">
-        <f>C362&amp;D362&amp;E362&amp;F362&amp;G362</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS361.PQTC.29.03.26</v>
       </c>
       <c r="L362" s="19" t="str">
-        <f>A362&amp;" "&amp;C362&amp;D362&amp;E362&amp;F362&amp;G362&amp;" "&amp;H362</f>
+        <f t="shared" si="14"/>
         <v>361 CupICARUS361.PQTC.29.03.26 ICARUS_Грибы</v>
       </c>
     </row>
@@ -14147,7 +14174,7 @@
         <v>426</v>
       </c>
       <c r="E363" s="6" t="str">
-        <f>A363&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>362.</v>
       </c>
       <c r="F363" s="19" t="s">
@@ -14160,11 +14187,11 @@
         <v>446</v>
       </c>
       <c r="J363" s="21" t="str">
-        <f>C363&amp;D363&amp;E363&amp;F363&amp;G363</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS362.PQTC.29.03.26</v>
       </c>
       <c r="L363" s="19" t="str">
-        <f>A363&amp;" "&amp;C363&amp;D363&amp;E363&amp;F363&amp;G363&amp;" "&amp;H363</f>
+        <f t="shared" si="14"/>
         <v>362 CupICARUS362.PQTC.29.03.26 ICARUS_Равнины</v>
       </c>
     </row>
@@ -14179,7 +14206,7 @@
         <v>426</v>
       </c>
       <c r="E364" s="6" t="str">
-        <f>A364&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>363.</v>
       </c>
       <c r="F364" s="19" t="s">
@@ -14192,11 +14219,11 @@
         <v>447</v>
       </c>
       <c r="J364" s="21" t="str">
-        <f>C364&amp;D364&amp;E364&amp;F364&amp;G364</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS363.PQTC.29.03.26</v>
       </c>
       <c r="L364" s="19" t="str">
-        <f>A364&amp;" "&amp;C364&amp;D364&amp;E364&amp;F364&amp;G364&amp;" "&amp;H364</f>
+        <f t="shared" si="14"/>
         <v>363 CupICARUS363.PQTC.29.03.26 ICARUS_Лава</v>
       </c>
     </row>
@@ -14211,7 +14238,7 @@
         <v>426</v>
       </c>
       <c r="E365" s="6" t="str">
-        <f>A365&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>364.</v>
       </c>
       <c r="F365" s="19" t="s">
@@ -14224,11 +14251,11 @@
         <v>448</v>
       </c>
       <c r="J365" s="21" t="str">
-        <f>C365&amp;D365&amp;E365&amp;F365&amp;G365</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS364.PQTC.29.03.26</v>
       </c>
       <c r="L365" s="19" t="str">
-        <f>A365&amp;" "&amp;C365&amp;D365&amp;E365&amp;F365&amp;G365&amp;" "&amp;H365</f>
+        <f t="shared" si="14"/>
         <v>364 CupICARUS364.PQTC.29.03.26 ICARUS_Лес</v>
       </c>
     </row>
@@ -14243,7 +14270,7 @@
         <v>426</v>
       </c>
       <c r="E366" s="6" t="str">
-        <f>A366&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>365.</v>
       </c>
       <c r="F366" s="19" t="s">
@@ -14256,11 +14283,11 @@
         <v>449</v>
       </c>
       <c r="J366" s="21" t="str">
-        <f>C366&amp;D366&amp;E366&amp;F366&amp;G366</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS365.PQTC.29.03.26</v>
       </c>
       <c r="L366" s="19" t="str">
-        <f>A366&amp;" "&amp;C366&amp;D366&amp;E366&amp;F366&amp;G366&amp;" "&amp;H366</f>
+        <f t="shared" si="14"/>
         <v>365 CupICARUS365.PQTC.29.03.26 ICARUS_Фауна</v>
       </c>
     </row>
@@ -14275,7 +14302,7 @@
         <v>426</v>
       </c>
       <c r="E367" s="6" t="str">
-        <f>A367&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>366.</v>
       </c>
       <c r="F367" s="19" t="s">
@@ -14288,12 +14315,332 @@
         <v>450</v>
       </c>
       <c r="J367" s="21" t="str">
-        <f>C367&amp;D367&amp;E367&amp;F367&amp;G367</f>
+        <f t="shared" si="13"/>
         <v>CupICARUS366.PQTC.29.03.26</v>
       </c>
       <c r="L367" s="19" t="str">
-        <f>A367&amp;" "&amp;C367&amp;D367&amp;E367&amp;F367&amp;G367&amp;" "&amp;H367</f>
+        <f t="shared" si="14"/>
         <v>366 CupICARUS366.PQTC.29.03.26 ICARUS_Горы</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12">
+      <c r="A368" s="5">
+        <v>367</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D368" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E368" s="6" t="str">
+        <f>A368&amp;"."</f>
+        <v>367.</v>
+      </c>
+      <c r="F368" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G368" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H368" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="J368" s="21" t="str">
+        <f>C368&amp;D368&amp;E368&amp;F368&amp;G368</f>
+        <v>NtrICARUS367.PQTC.30.03.26</v>
+      </c>
+      <c r="L368" s="19" t="str">
+        <f>A368&amp;" "&amp;C368&amp;D368&amp;E368&amp;F368&amp;G368&amp;" "&amp;H368</f>
+        <v>367 NtrICARUS367.PQTC.30.03.26 ICARUS_Сердце</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12">
+      <c r="A369" s="5">
+        <v>368</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D369" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E369" s="6" t="str">
+        <f>A369&amp;"."</f>
+        <v>368.</v>
+      </c>
+      <c r="F369" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G369" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H369" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="J369" s="21" t="str">
+        <f>C369&amp;D369&amp;E369&amp;F369&amp;G369</f>
+        <v>NtrICARUS368.PQTC.30.03.26</v>
+      </c>
+      <c r="L369" s="19" t="str">
+        <f>A369&amp;" "&amp;C369&amp;D369&amp;E369&amp;F369&amp;G369&amp;" "&amp;H369</f>
+        <v>368 NtrICARUS368.PQTC.30.03.26 ICARUS_Медведь</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12">
+      <c r="A370" s="5">
+        <v>369</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D370" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E370" s="6" t="str">
+        <f>A370&amp;"."</f>
+        <v>369.</v>
+      </c>
+      <c r="F370" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G370" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H370" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="J370" s="21" t="str">
+        <f>C370&amp;D370&amp;E370&amp;F370&amp;G370</f>
+        <v>NtrICARUS369.PQTC.30.03.26</v>
+      </c>
+      <c r="L370" s="19" t="str">
+        <f>A370&amp;" "&amp;C370&amp;D370&amp;E370&amp;F370&amp;G370&amp;" "&amp;H370</f>
+        <v>369 NtrICARUS369.PQTC.30.03.26 ICARUS_Астронавты</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12">
+      <c r="A371" s="5">
+        <v>370</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E371" s="6" t="str">
+        <f>A371&amp;"."</f>
+        <v>370.</v>
+      </c>
+      <c r="F371" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G371" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H371" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="J371" s="21" t="str">
+        <f>C371&amp;D371&amp;E371&amp;F371&amp;G371</f>
+        <v>NtrICARUS370.PQTC.30.03.26</v>
+      </c>
+      <c r="L371" s="19" t="str">
+        <f>A371&amp;" "&amp;C371&amp;D371&amp;E371&amp;F371&amp;G371&amp;" "&amp;H371</f>
+        <v>370 NtrICARUS370.PQTC.30.03.26 ICARUS_Лагерь</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12">
+      <c r="A372" s="5">
+        <v>371</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E372" s="6" t="str">
+        <f>A372&amp;"."</f>
+        <v>371.</v>
+      </c>
+      <c r="F372" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G372" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H372" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="J372" s="21" t="str">
+        <f>C372&amp;D372&amp;E372&amp;F372&amp;G372</f>
+        <v>NtrICARUS371.PQTC.30.03.26</v>
+      </c>
+      <c r="L372" s="19" t="str">
+        <f>A372&amp;" "&amp;C372&amp;D372&amp;E372&amp;F372&amp;G372&amp;" "&amp;H372</f>
+        <v>371 NtrICARUS371.PQTC.30.03.26 ICARUS_Верстак</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12">
+      <c r="A373" s="5">
+        <v>372</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E373" s="6" t="str">
+        <f>A373&amp;"."</f>
+        <v>372.</v>
+      </c>
+      <c r="F373" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G373" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H373" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="J373" s="21" t="str">
+        <f>C373&amp;D373&amp;E373&amp;F373&amp;G373</f>
+        <v>NtrICARUS372.PQTC.30.03.26</v>
+      </c>
+      <c r="L373" s="19" t="str">
+        <f>A373&amp;" "&amp;C373&amp;D373&amp;E373&amp;F373&amp;G373&amp;" "&amp;H373</f>
+        <v>372 NtrICARUS372.PQTC.30.03.26 ICARUS_Космос</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12">
+      <c r="A374" s="5">
+        <v>373</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E374" s="6" t="str">
+        <f>A374&amp;"."</f>
+        <v>373.</v>
+      </c>
+      <c r="F374" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G374" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H374" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="J374" s="21" t="str">
+        <f>C374&amp;D374&amp;E374&amp;F374&amp;G374</f>
+        <v>NtrICARUS373.PQTC.30.03.26</v>
+      </c>
+      <c r="L374" s="19" t="str">
+        <f>A374&amp;" "&amp;C374&amp;D374&amp;E374&amp;F374&amp;G374&amp;" "&amp;H374</f>
+        <v>373 NtrICARUS373.PQTC.30.03.26 ICARUS_Олень</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12">
+      <c r="A375" s="5">
+        <v>374</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E375" s="6" t="str">
+        <f>A375&amp;"."</f>
+        <v>374.</v>
+      </c>
+      <c r="F375" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G375" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H375" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="J375" s="21" t="str">
+        <f>C375&amp;D375&amp;E375&amp;F375&amp;G375</f>
+        <v>NtrICARUS374.PQTC.30.03.26</v>
+      </c>
+      <c r="L375" s="19" t="str">
+        <f>A375&amp;" "&amp;C375&amp;D375&amp;E375&amp;F375&amp;G375&amp;" "&amp;H375</f>
+        <v>374 NtrICARUS374.PQTC.30.03.26 ICARUS_Грибы</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12">
+      <c r="A376" s="5">
+        <v>375</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E376" s="6" t="str">
+        <f>A376&amp;"."</f>
+        <v>375.</v>
+      </c>
+      <c r="F376" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G376" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H376" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="J376" s="21" t="str">
+        <f>C376&amp;D376&amp;E376&amp;F376&amp;G376</f>
+        <v>NtrICARUS375.PQTC.30.03.26</v>
+      </c>
+      <c r="L376" s="19" t="str">
+        <f>A376&amp;" "&amp;C376&amp;D376&amp;E376&amp;F376&amp;G376&amp;" "&amp;H376</f>
+        <v>375 NtrICARUS375.PQTC.30.03.26 ICARUS_Оазис</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12">
+      <c r="A377" s="5">
+        <v>376</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D377" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E377" s="6" t="str">
+        <f>A377&amp;"."</f>
+        <v>376.</v>
+      </c>
+      <c r="F377" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G377" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="H377" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="J377" s="21" t="str">
+        <f>C377&amp;D377&amp;E377&amp;F377&amp;G377</f>
+        <v>NtrICARUS376.PQTC.30.03.26</v>
+      </c>
+      <c r="L377" s="19" t="str">
+        <f>A377&amp;" "&amp;C377&amp;D377&amp;E377&amp;F377&amp;G377&amp;" "&amp;H377</f>
+        <v>376 NtrICARUS376.PQTC.30.03.26 ICARUS_Луга</v>
       </c>
     </row>
   </sheetData>
@@ -14342,136 +14689,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9.10526315789474" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9.10185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="45.1052631578947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.8859649122807" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.10526315789474" style="1"/>
+    <col min="1" max="1" width="45.1018518518519" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.10185185185185" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" ht="16.35" spans="1:2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -14479,23 +14826,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -14503,23 +14850,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -14527,39 +14874,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -14567,162 +14914,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>

--- a/Таблица с артикулам.xlsx
+++ b/Таблица с артикулам.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Артикулы" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="553">
   <si>
     <t>Номер баннера</t>
   </si>
@@ -1396,6 +1396,27 @@
   </si>
   <si>
     <t>ICARUS_Луга</t>
+  </si>
+  <si>
+    <t>31.03.26</t>
+  </si>
+  <si>
+    <t>ICARUS_Метель</t>
+  </si>
+  <si>
+    <t>ICARUS_Астронавт</t>
+  </si>
+  <si>
+    <t>ICARUS_Медведи</t>
+  </si>
+  <si>
+    <t>ICARUS_Выстрел</t>
+  </si>
+  <si>
+    <t>ICARUS_Пещера</t>
+  </si>
+  <si>
+    <t>ICARUS_Водопад</t>
   </si>
   <si>
     <t>Товар</t>
@@ -1678,7 +1699,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1731,6 +1752,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2223,16 +2250,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2241,115 +2265,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2419,12 +2446,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2695,23 +2720,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q377"/>
+  <dimension ref="A1:Q387"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.8859649122807" style="5" customWidth="1"/>
     <col min="2" max="2" width="3.66666666666667" style="6" customWidth="1"/>
     <col min="3" max="3" width="15.3333333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.4351851851852" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.5555555555556" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.4385964912281" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.5526315789474" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.3333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="9.88888888888889" style="8" customWidth="1"/>
-    <col min="8" max="8" width="28.1018518518519" style="6" customWidth="1"/>
-    <col min="9" max="9" width="7.55555555555556" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.8859649122807" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.1052631578947" style="6" customWidth="1"/>
+    <col min="9" max="9" width="7.55263157894737" style="6" customWidth="1"/>
     <col min="10" max="10" width="29.6666666666667" style="6" customWidth="1"/>
     <col min="11" max="11" width="10" style="6"/>
-    <col min="12" max="12" width="66.8888888888889" style="6" customWidth="1"/>
+    <col min="12" max="12" width="66.8859649122807" style="6" customWidth="1"/>
     <col min="13" max="15" width="10" style="6"/>
-    <col min="16" max="16" width="8.88888888888889" style="6" customWidth="1"/>
+    <col min="16" max="16" width="8.8859649122807" style="6" customWidth="1"/>
     <col min="17" max="16384" width="10" style="6"/>
   </cols>
   <sheetData>
@@ -12670,7 +12695,7 @@
         <v>397</v>
       </c>
       <c r="E316" s="6" t="str">
-        <f t="shared" ref="E316:E367" si="12">A316&amp;"."</f>
+        <f t="shared" ref="E316:E377" si="12">A316&amp;"."</f>
         <v>315.</v>
       </c>
       <c r="F316" s="19" t="s">
@@ -12875,11 +12900,11 @@
         <v>407</v>
       </c>
       <c r="J322" s="21" t="str">
-        <f t="shared" ref="J322:J367" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
+        <f t="shared" ref="J322:J377" si="13">C322&amp;D322&amp;E322&amp;F322&amp;G322</f>
         <v>CupDontSt321.PQTC.26.03.26</v>
       </c>
       <c r="L322" s="19" t="str">
-        <f t="shared" ref="L322:L367" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
+        <f t="shared" ref="L322:L377" si="14">A322&amp;" "&amp;C322&amp;D322&amp;E322&amp;F322&amp;G322&amp;" "&amp;H322</f>
         <v>321 CupDontSt321.PQTC.26.03.26 Обложка_Verdant</v>
       </c>
     </row>
@@ -14334,7 +14359,7 @@
         <v>426</v>
       </c>
       <c r="E368" s="6" t="str">
-        <f>A368&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>367.</v>
       </c>
       <c r="F368" s="19" t="s">
@@ -14343,15 +14368,15 @@
       <c r="G368" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H368" s="23" t="s">
+      <c r="H368" s="19" t="s">
         <v>439</v>
       </c>
       <c r="J368" s="21" t="str">
-        <f>C368&amp;D368&amp;E368&amp;F368&amp;G368</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS367.PQTC.30.03.26</v>
       </c>
       <c r="L368" s="19" t="str">
-        <f>A368&amp;" "&amp;C368&amp;D368&amp;E368&amp;F368&amp;G368&amp;" "&amp;H368</f>
+        <f t="shared" si="14"/>
         <v>367 NtrICARUS367.PQTC.30.03.26 ICARUS_Сердце</v>
       </c>
     </row>
@@ -14366,7 +14391,7 @@
         <v>426</v>
       </c>
       <c r="E369" s="6" t="str">
-        <f>A369&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>368.</v>
       </c>
       <c r="F369" s="19" t="s">
@@ -14375,15 +14400,15 @@
       <c r="G369" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H369" s="23" t="s">
+      <c r="H369" s="19" t="s">
         <v>440</v>
       </c>
       <c r="J369" s="21" t="str">
-        <f>C369&amp;D369&amp;E369&amp;F369&amp;G369</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS368.PQTC.30.03.26</v>
       </c>
       <c r="L369" s="19" t="str">
-        <f>A369&amp;" "&amp;C369&amp;D369&amp;E369&amp;F369&amp;G369&amp;" "&amp;H369</f>
+        <f t="shared" si="14"/>
         <v>368 NtrICARUS368.PQTC.30.03.26 ICARUS_Медведь</v>
       </c>
     </row>
@@ -14398,7 +14423,7 @@
         <v>426</v>
       </c>
       <c r="E370" s="6" t="str">
-        <f>A370&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>369.</v>
       </c>
       <c r="F370" s="19" t="s">
@@ -14407,15 +14432,15 @@
       <c r="G370" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H370" s="23" t="s">
+      <c r="H370" s="19" t="s">
         <v>441</v>
       </c>
       <c r="J370" s="21" t="str">
-        <f>C370&amp;D370&amp;E370&amp;F370&amp;G370</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS369.PQTC.30.03.26</v>
       </c>
       <c r="L370" s="19" t="str">
-        <f>A370&amp;" "&amp;C370&amp;D370&amp;E370&amp;F370&amp;G370&amp;" "&amp;H370</f>
+        <f t="shared" si="14"/>
         <v>369 NtrICARUS369.PQTC.30.03.26 ICARUS_Астронавты</v>
       </c>
     </row>
@@ -14430,7 +14455,7 @@
         <v>426</v>
       </c>
       <c r="E371" s="6" t="str">
-        <f>A371&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>370.</v>
       </c>
       <c r="F371" s="19" t="s">
@@ -14439,15 +14464,15 @@
       <c r="G371" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H371" s="23" t="s">
+      <c r="H371" s="19" t="s">
         <v>452</v>
       </c>
       <c r="J371" s="21" t="str">
-        <f>C371&amp;D371&amp;E371&amp;F371&amp;G371</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS370.PQTC.30.03.26</v>
       </c>
       <c r="L371" s="19" t="str">
-        <f>A371&amp;" "&amp;C371&amp;D371&amp;E371&amp;F371&amp;G371&amp;" "&amp;H371</f>
+        <f t="shared" si="14"/>
         <v>370 NtrICARUS370.PQTC.30.03.26 ICARUS_Лагерь</v>
       </c>
     </row>
@@ -14462,7 +14487,7 @@
         <v>426</v>
       </c>
       <c r="E372" s="6" t="str">
-        <f>A372&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>371.</v>
       </c>
       <c r="F372" s="19" t="s">
@@ -14471,15 +14496,15 @@
       <c r="G372" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H372" s="24" t="s">
+      <c r="H372" s="23" t="s">
         <v>444</v>
       </c>
       <c r="J372" s="21" t="str">
-        <f>C372&amp;D372&amp;E372&amp;F372&amp;G372</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS371.PQTC.30.03.26</v>
       </c>
       <c r="L372" s="19" t="str">
-        <f>A372&amp;" "&amp;C372&amp;D372&amp;E372&amp;F372&amp;G372&amp;" "&amp;H372</f>
+        <f t="shared" si="14"/>
         <v>371 NtrICARUS371.PQTC.30.03.26 ICARUS_Верстак</v>
       </c>
     </row>
@@ -14494,7 +14519,7 @@
         <v>426</v>
       </c>
       <c r="E373" s="6" t="str">
-        <f>A373&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>372.</v>
       </c>
       <c r="F373" s="19" t="s">
@@ -14503,15 +14528,15 @@
       <c r="G373" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H373" s="24" t="s">
+      <c r="H373" s="23" t="s">
         <v>453</v>
       </c>
       <c r="J373" s="21" t="str">
-        <f>C373&amp;D373&amp;E373&amp;F373&amp;G373</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS372.PQTC.30.03.26</v>
       </c>
       <c r="L373" s="19" t="str">
-        <f>A373&amp;" "&amp;C373&amp;D373&amp;E373&amp;F373&amp;G373&amp;" "&amp;H373</f>
+        <f t="shared" si="14"/>
         <v>372 NtrICARUS372.PQTC.30.03.26 ICARUS_Космос</v>
       </c>
     </row>
@@ -14526,7 +14551,7 @@
         <v>426</v>
       </c>
       <c r="E374" s="6" t="str">
-        <f>A374&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>373.</v>
       </c>
       <c r="F374" s="19" t="s">
@@ -14535,15 +14560,15 @@
       <c r="G374" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H374" s="24" t="s">
+      <c r="H374" s="23" t="s">
         <v>454</v>
       </c>
       <c r="J374" s="21" t="str">
-        <f>C374&amp;D374&amp;E374&amp;F374&amp;G374</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS373.PQTC.30.03.26</v>
       </c>
       <c r="L374" s="19" t="str">
-        <f>A374&amp;" "&amp;C374&amp;D374&amp;E374&amp;F374&amp;G374&amp;" "&amp;H374</f>
+        <f t="shared" si="14"/>
         <v>373 NtrICARUS373.PQTC.30.03.26 ICARUS_Олень</v>
       </c>
     </row>
@@ -14558,7 +14583,7 @@
         <v>426</v>
       </c>
       <c r="E375" s="6" t="str">
-        <f>A375&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>374.</v>
       </c>
       <c r="F375" s="19" t="s">
@@ -14567,15 +14592,15 @@
       <c r="G375" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H375" s="24" t="s">
+      <c r="H375" s="23" t="s">
         <v>445</v>
       </c>
       <c r="J375" s="21" t="str">
-        <f>C375&amp;D375&amp;E375&amp;F375&amp;G375</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS374.PQTC.30.03.26</v>
       </c>
       <c r="L375" s="19" t="str">
-        <f>A375&amp;" "&amp;C375&amp;D375&amp;E375&amp;F375&amp;G375&amp;" "&amp;H375</f>
+        <f t="shared" si="14"/>
         <v>374 NtrICARUS374.PQTC.30.03.26 ICARUS_Грибы</v>
       </c>
     </row>
@@ -14590,7 +14615,7 @@
         <v>426</v>
       </c>
       <c r="E376" s="6" t="str">
-        <f>A376&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>375.</v>
       </c>
       <c r="F376" s="19" t="s">
@@ -14599,15 +14624,15 @@
       <c r="G376" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H376" s="24" t="s">
+      <c r="H376" s="23" t="s">
         <v>442</v>
       </c>
       <c r="J376" s="21" t="str">
-        <f>C376&amp;D376&amp;E376&amp;F376&amp;G376</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS375.PQTC.30.03.26</v>
       </c>
       <c r="L376" s="19" t="str">
-        <f>A376&amp;" "&amp;C376&amp;D376&amp;E376&amp;F376&amp;G376&amp;" "&amp;H376</f>
+        <f t="shared" si="14"/>
         <v>375 NtrICARUS375.PQTC.30.03.26 ICARUS_Оазис</v>
       </c>
     </row>
@@ -14622,7 +14647,7 @@
         <v>426</v>
       </c>
       <c r="E377" s="6" t="str">
-        <f>A377&amp;"."</f>
+        <f t="shared" si="12"/>
         <v>376.</v>
       </c>
       <c r="F377" s="19" t="s">
@@ -14631,16 +14656,336 @@
       <c r="G377" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="H377" s="24" t="s">
+      <c r="H377" s="23" t="s">
         <v>455</v>
       </c>
       <c r="J377" s="21" t="str">
-        <f>C377&amp;D377&amp;E377&amp;F377&amp;G377</f>
+        <f t="shared" si="13"/>
         <v>NtrICARUS376.PQTC.30.03.26</v>
       </c>
       <c r="L377" s="19" t="str">
-        <f>A377&amp;" "&amp;C377&amp;D377&amp;E377&amp;F377&amp;G377&amp;" "&amp;H377</f>
+        <f t="shared" si="14"/>
         <v>376 NtrICARUS376.PQTC.30.03.26 ICARUS_Луга</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12">
+      <c r="A378" s="5">
+        <v>377</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E378" s="6" t="str">
+        <f>A378&amp;"."</f>
+        <v>377.</v>
+      </c>
+      <c r="F378" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G378" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H378" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="J378" s="21" t="str">
+        <f>C378&amp;D378&amp;E378&amp;F378&amp;G378</f>
+        <v>OpsICARUS377.PQTC.31.03.26</v>
+      </c>
+      <c r="L378" s="19" t="str">
+        <f>A378&amp;" "&amp;C378&amp;D378&amp;E378&amp;F378&amp;G378&amp;" "&amp;H378</f>
+        <v>377 OpsICARUS377.PQTC.31.03.26 ICARUS_Олень</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12">
+      <c r="A379" s="5">
+        <v>378</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E379" s="6" t="str">
+        <f>A379&amp;"."</f>
+        <v>378.</v>
+      </c>
+      <c r="F379" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G379" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H379" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="J379" s="21" t="str">
+        <f>C379&amp;D379&amp;E379&amp;F379&amp;G379</f>
+        <v>OpsICARUS378.PQTC.31.03.26</v>
+      </c>
+      <c r="L379" s="19" t="str">
+        <f>A379&amp;" "&amp;C379&amp;D379&amp;E379&amp;F379&amp;G379&amp;" "&amp;H379</f>
+        <v>378 OpsICARUS378.PQTC.31.03.26 ICARUS_Метель</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12">
+      <c r="A380" s="5">
+        <v>379</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E380" s="6" t="str">
+        <f>A380&amp;"."</f>
+        <v>379.</v>
+      </c>
+      <c r="F380" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G380" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H380" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="J380" s="21" t="str">
+        <f>C380&amp;D380&amp;E380&amp;F380&amp;G380</f>
+        <v>OpsICARUS379.PQTC.31.03.26</v>
+      </c>
+      <c r="L380" s="19" t="str">
+        <f>A380&amp;" "&amp;C380&amp;D380&amp;E380&amp;F380&amp;G380&amp;" "&amp;H380</f>
+        <v>379 OpsICARUS379.PQTC.31.03.26 ICARUS_Астронавт</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12">
+      <c r="A381" s="5">
+        <v>380</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E381" s="6" t="str">
+        <f>A381&amp;"."</f>
+        <v>380.</v>
+      </c>
+      <c r="F381" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G381" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H381" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="J381" s="21" t="str">
+        <f>C381&amp;D381&amp;E381&amp;F381&amp;G381</f>
+        <v>OpsICARUS380.PQTC.31.03.26</v>
+      </c>
+      <c r="L381" s="19" t="str">
+        <f>A381&amp;" "&amp;C381&amp;D381&amp;E381&amp;F381&amp;G381&amp;" "&amp;H381</f>
+        <v>380 OpsICARUS380.PQTC.31.03.26 ICARUS_Медведи</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12">
+      <c r="A382" s="5">
+        <v>381</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D382" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E382" s="6" t="str">
+        <f>A382&amp;"."</f>
+        <v>381.</v>
+      </c>
+      <c r="F382" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G382" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H382" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="J382" s="21" t="str">
+        <f>C382&amp;D382&amp;E382&amp;F382&amp;G382</f>
+        <v>OpsICARUS381.PQTC.31.03.26</v>
+      </c>
+      <c r="L382" s="19" t="str">
+        <f>A382&amp;" "&amp;C382&amp;D382&amp;E382&amp;F382&amp;G382&amp;" "&amp;H382</f>
+        <v>381 OpsICARUS381.PQTC.31.03.26 ICARUS_Лагерь</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12">
+      <c r="A383" s="5">
+        <v>382</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E383" s="6" t="str">
+        <f>A383&amp;"."</f>
+        <v>382.</v>
+      </c>
+      <c r="F383" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G383" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H383" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="J383" s="21" t="str">
+        <f>C383&amp;D383&amp;E383&amp;F383&amp;G383</f>
+        <v>OpsICARUS382.PQTC.31.03.26</v>
+      </c>
+      <c r="L383" s="19" t="str">
+        <f>A383&amp;" "&amp;C383&amp;D383&amp;E383&amp;F383&amp;G383&amp;" "&amp;H383</f>
+        <v>382 OpsICARUS382.PQTC.31.03.26 ICARUS_Грибы</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12">
+      <c r="A384" s="5">
+        <v>383</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D384" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E384" s="6" t="str">
+        <f>A384&amp;"."</f>
+        <v>383.</v>
+      </c>
+      <c r="F384" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G384" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H384" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="J384" s="21" t="str">
+        <f>C384&amp;D384&amp;E384&amp;F384&amp;G384</f>
+        <v>OpsICARUS383.PQTC.31.03.26</v>
+      </c>
+      <c r="L384" s="19" t="str">
+        <f>A384&amp;" "&amp;C384&amp;D384&amp;E384&amp;F384&amp;G384&amp;" "&amp;H384</f>
+        <v>383 OpsICARUS383.PQTC.31.03.26 ICARUS_Верстак</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12">
+      <c r="A385" s="5">
+        <v>384</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E385" s="6" t="str">
+        <f>A385&amp;"."</f>
+        <v>384.</v>
+      </c>
+      <c r="F385" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G385" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H385" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="J385" s="21" t="str">
+        <f>C385&amp;D385&amp;E385&amp;F385&amp;G385</f>
+        <v>OpsICARUS384.PQTC.31.03.26</v>
+      </c>
+      <c r="L385" s="19" t="str">
+        <f>A385&amp;" "&amp;C385&amp;D385&amp;E385&amp;F385&amp;G385&amp;" "&amp;H385</f>
+        <v>384 OpsICARUS384.PQTC.31.03.26 ICARUS_Выстрел</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12">
+      <c r="A386" s="5">
+        <v>385</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E386" s="6" t="str">
+        <f>A386&amp;"."</f>
+        <v>385.</v>
+      </c>
+      <c r="F386" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G386" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H386" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="J386" s="21" t="str">
+        <f>C386&amp;D386&amp;E386&amp;F386&amp;G386</f>
+        <v>OpsICARUS385.PQTC.31.03.26</v>
+      </c>
+      <c r="L386" s="19" t="str">
+        <f>A386&amp;" "&amp;C386&amp;D386&amp;E386&amp;F386&amp;G386&amp;" "&amp;H386</f>
+        <v>385 OpsICARUS385.PQTC.31.03.26 ICARUS_Пещера</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12">
+      <c r="A387" s="5">
+        <v>386</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E387" s="6" t="str">
+        <f>A387&amp;"."</f>
+        <v>386.</v>
+      </c>
+      <c r="F387" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G387" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H387" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="J387" s="21" t="str">
+        <f>C387&amp;D387&amp;E387&amp;F387&amp;G387</f>
+        <v>OpsICARUS386.PQTC.31.03.26</v>
+      </c>
+      <c r="L387" s="19" t="str">
+        <f>A387&amp;" "&amp;C387&amp;D387&amp;E387&amp;F387&amp;G387&amp;" "&amp;H387</f>
+        <v>386 OpsICARUS386.PQTC.31.03.26 ICARUS_Водопад</v>
       </c>
     </row>
   </sheetData>
@@ -14689,136 +15034,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultColWidth="9.10185185185185" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9.10526315789474" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="45.1018518518519" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.10185185185185" style="1"/>
+    <col min="1" max="1" width="45.1052631578947" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.8859649122807" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.10526315789474" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.35" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" ht="16.35" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" ht="16.35" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" ht="16.35" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="5" ht="31.95" spans="1:2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="5" ht="16.35" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" ht="16.35" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" ht="16.35" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" ht="16.35" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" ht="16.35" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" ht="16.35" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" ht="16.35" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" ht="16.35" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" ht="16.35" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" ht="16.35" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" ht="16.35" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" ht="16.35" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>19</v>
@@ -14826,23 +15171,23 @@
     </row>
     <row r="17" ht="16.35" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" ht="16.35" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" ht="16.35" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>246</v>
@@ -14850,23 +15195,23 @@
     </row>
     <row r="20" ht="16.35" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" ht="16.35" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" ht="16.35" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>10</v>
@@ -14874,39 +15219,39 @@
     </row>
     <row r="23" ht="16.35" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" ht="16.35" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" ht="16.35" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" ht="16.35" spans="1:2">
       <c r="A26" s="3" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="27" ht="16.35" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -14914,162 +15259,162 @@
     </row>
     <row r="28" ht="16.35" spans="1:2">
       <c r="A28" s="3" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" ht="16.35" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="30" ht="16.35" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" ht="16.35" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" ht="16.35" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33" ht="16.35" spans="1:2">
       <c r="A33" s="4" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="34" ht="16.35" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="35" ht="16.35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:2">
       <c r="A36" s="4" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" ht="16.35" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" ht="16.35" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" ht="16.35" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" ht="16.35" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" ht="16.35" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="43" ht="16.35" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="44" ht="16.35" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="45" ht="16.35" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="46" ht="16.35" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="47" ht="16.35" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
